--- a/database/event/2248/event_2248_evp_summary.xlsx
+++ b/database/event/2248/event_2248_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.8742</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2324</v>
+        <v>3.1594</v>
       </c>
       <c r="E2" t="n">
         <v>9.0444</v>
@@ -548,7 +548,7 @@
         <v>3.1486</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5481</v>
+        <v>2.4845</v>
       </c>
       <c r="E3" t="n">
         <v>7.3505</v>
@@ -594,7 +594,7 @@
         <v>2.7379</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1607</v>
+        <v>2.1025</v>
       </c>
       <c r="E4" t="n">
         <v>6.3916</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2947</v>
+        <v>3.3767</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4113</v>
+        <v>1.4464</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9096</v>
+        <v>0.9014</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2947</v>
+        <v>3.3767</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2596</v>
+        <v>4.3416</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9649</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5767</v>
+        <v>4.9068</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7096</v>
+        <v>3.9771</v>
       </c>
       <c r="J5" t="n">
         <v>-0.9649</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7447</v>
+        <v>3.0122</v>
       </c>
       <c r="N5" t="n">
         <v>157</v>
@@ -686,7 +686,7 @@
         <v>1.2017</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7119</v>
+        <v>0.6737</v>
       </c>
       <c r="E6" t="n">
         <v>2.8053</v>
@@ -732,7 +732,7 @@
         <v>1.0862</v>
       </c>
       <c r="D7" t="n">
-        <v>0.603</v>
+        <v>0.5663</v>
       </c>
       <c r="E7" t="n">
         <v>2.5357</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9948</v>
+        <v>2.0791</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8545</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3845</v>
+        <v>0.3844</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9948</v>
+        <v>2.0791</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2861</v>
+        <v>0.7294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7087</v>
+        <v>1.3497</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2861</v>
+        <v>0.7294</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0424</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7087</v>
+        <v>1.3497</v>
       </c>
       <c r="K8" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7511</v>
+        <v>1.9409</v>
       </c>
       <c r="N8" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9531</v>
+        <v>1.9948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8366</v>
+        <v>0.8545</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3676</v>
+        <v>0.3508</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9531</v>
+        <v>1.9948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6034</v>
+        <v>1.2861</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3497</v>
+        <v>0.7087</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6034</v>
+        <v>1.2861</v>
       </c>
       <c r="I9" t="n">
-        <v>0.489</v>
+        <v>1.0424</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3497</v>
+        <v>0.7087</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8387</v>
+        <v>1.7511</v>
       </c>
       <c r="N9" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -870,7 +870,7 @@
         <v>0.7723</v>
       </c>
       <c r="D10" t="n">
-        <v>0.307</v>
+        <v>0.2744</v>
       </c>
       <c r="E10" t="n">
         <v>1.8029</v>
@@ -916,7 +916,7 @@
         <v>0.7671</v>
       </c>
       <c r="D11" t="n">
-        <v>0.302</v>
+        <v>0.2695</v>
       </c>
       <c r="E11" t="n">
         <v>1.7907</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3556</v>
+        <v>1.4814</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5807</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1263</v>
+        <v>0.1463</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3556</v>
+        <v>1.4814</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8128</v>
+        <v>1.9386</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4572</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8128</v>
+        <v>1.9386</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4694</v>
+        <v>1.5713</v>
       </c>
       <c r="J12" t="n">
         <v>-0.4572</v>
@@ -989,7 +989,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0122</v>
+        <v>1.1141</v>
       </c>
       <c r="N12" t="n">
         <v>106</v>
@@ -1008,7 +1008,7 @@
         <v>0.5697</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1159</v>
+        <v>0.0859</v>
       </c>
       <c r="E13" t="n">
         <v>1.3299</v>
@@ -1044,124 +1044,124 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1804</v>
+        <v>1.2455</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5056</v>
+        <v>0.5335</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0555</v>
+        <v>0.0523</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1804</v>
+        <v>1.2455</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1804</v>
+        <v>1.3991</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.1536</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1804</v>
+        <v>1.3991</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1804</v>
+        <v>1.134</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.1536</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1804</v>
+        <v>0.9803999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0671</v>
+        <v>1.2194</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4571</v>
+        <v>0.5223</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0097</v>
+        <v>0.0419</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0671</v>
+        <v>1.2194</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0671</v>
+        <v>1.3436</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.1242</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0671</v>
+        <v>1.3436</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0671</v>
+        <v>1.089</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.1242</v>
       </c>
       <c r="K15" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0671</v>
+        <v>0.9648</v>
       </c>
       <c r="N15" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4159</v>
+        <v>0.5056</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0291</v>
+        <v>0.0264</v>
       </c>
       <c r="E16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="F16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="I16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.971</v>
+        <v>1.1804</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4076</v>
+        <v>0.4571</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.037</v>
+        <v>-0.0188</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9515</v>
+        <v>1.0671</v>
       </c>
       <c r="N17" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9333</v>
+        <v>0.971</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3998</v>
+        <v>0.4159</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0443</v>
+        <v>-0.0571</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9333</v>
+        <v>0.971</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0575</v>
+        <v>0.971</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0575</v>
+        <v>0.971</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8572</v>
+        <v>0.971</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.733</v>
+        <v>0.971</v>
       </c>
       <c r="N18" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3909</v>
+        <v>0.4076</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0527</v>
+        <v>-0.0648</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9125</v>
+        <v>0.9515</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8176</v>
+        <v>0.9125</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3502</v>
+        <v>0.3909</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0911</v>
+        <v>-0.0804</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8176</v>
+        <v>0.9125</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9712</v>
+        <v>0.9125</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1536</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9712</v>
+        <v>0.9125</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7872</v>
+        <v>0.9125</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1536</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L20" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.9125</v>
       </c>
       <c r="N20" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2602</v>
+        <v>0.3698</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1759</v>
+        <v>-0.0999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6075</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>127</v>
@@ -1422,7 +1422,7 @@
         <v>0.1938</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2386</v>
+        <v>-0.2636</v>
       </c>
       <c r="E22" t="n">
         <v>0.4525</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4175</v>
+        <v>0.4194</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1788</v>
+        <v>0.1797</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2527</v>
+        <v>-0.2768</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4175</v>
+        <v>0.4194</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2337</v>
+        <v>1.2356</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8162</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2337</v>
+        <v>1.2356</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9999</v>
+        <v>1.0015</v>
       </c>
       <c r="J23" t="n">
         <v>-0.8162</v>
@@ -1495,7 +1495,7 @@
         <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1837</v>
+        <v>0.1853</v>
       </c>
       <c r="N23" t="n">
         <v>106</v>
@@ -1514,7 +1514,7 @@
         <v>0.1721</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2591</v>
+        <v>-0.2839</v>
       </c>
       <c r="E24" t="n">
         <v>0.4017</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2645</v>
+        <v>0.3499</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1133</v>
+        <v>0.1499</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3145</v>
+        <v>-0.3045</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2645</v>
+        <v>0.3499</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4979</v>
+        <v>0.5833</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2334</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4979</v>
+        <v>0.5833</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4035</v>
+        <v>0.4728</v>
       </c>
       <c r="J25" t="n">
         <v>-0.2334</v>
@@ -1587,7 +1587,7 @@
         <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1701</v>
+        <v>0.2394</v>
       </c>
       <c r="N25" t="n">
         <v>106</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEMPHIS</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2525</v>
+        <v>0.2658</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1082</v>
+        <v>0.1139</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3194</v>
+        <v>-0.338</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2525</v>
+        <v>0.2658</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9766</v>
+        <v>0.2658</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9766</v>
+        <v>0.2658</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7916</v>
+        <v>0.2658</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0675</v>
+        <v>0.2658</v>
       </c>
       <c r="N26" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>SEMPHIS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2113</v>
+        <v>0.2525</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0905</v>
+        <v>0.1082</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.336</v>
+        <v>-0.3433</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2113</v>
+        <v>0.2525</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2113</v>
+        <v>0.9766</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.7241</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2113</v>
+        <v>0.9766</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2113</v>
+        <v>0.7916</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.7241</v>
       </c>
       <c r="K27" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2113</v>
+        <v>0.0675</v>
       </c>
       <c r="N27" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>-0.0066</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4276</v>
+        <v>-0.4501</v>
       </c>
       <c r="E28" t="n">
         <v>-0.0155</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0465</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4887</v>
+        <v>-0.4871</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1668</v>
+        <v>-0.1085</v>
       </c>
       <c r="N29" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2292</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6375</v>
+        <v>-0.5104</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5351</v>
+        <v>-0.1668</v>
       </c>
       <c r="N30" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
@@ -1836,7 +1836,7 @@
         <v>-0.3472</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7488</v>
+        <v>-0.7668</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8105</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3583</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7593</v>
+        <v>-0.7772</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8365</v>
@@ -1928,7 +1928,7 @@
         <v>-0.367</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7675</v>
+        <v>-0.7852</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8567</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0446</v>
+        <v>-0.9724</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4475</v>
+        <v>-0.4165</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8434</v>
+        <v>-0.8313</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0446</v>
+        <v>-0.9724</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0446</v>
+        <v>-0.2165</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.7559</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0446</v>
+        <v>-0.2165</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0446</v>
+        <v>-0.1755</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.7559</v>
       </c>
       <c r="K34" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0446</v>
+        <v>-0.9314</v>
       </c>
       <c r="N34" t="n">
-        <v>74</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1278</v>
+        <v>-1.0446</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4831</v>
+        <v>-0.4475</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.877</v>
+        <v>-0.8601</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1278</v>
+        <v>-1.0446</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3719</v>
+        <v>-1.0446</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7559</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3719</v>
+        <v>-1.0446</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3015</v>
+        <v>-1.0446</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7559</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="L35" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0574</v>
+        <v>-1.0446</v>
       </c>
       <c r="N35" t="n">
-        <v>157</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
@@ -2066,7 +2066,7 @@
         <v>-0.5002</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8931</v>
+        <v>-0.9091</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1677</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5158</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9237</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2042</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5467</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9524</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2764</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5566</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9463</v>
+        <v>-0.9616</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2993</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8857</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2567</v>
+        <v>-1.2677</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0677</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8941</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2646</v>
+        <v>-1.2755</v>
       </c>
       <c r="E41" t="n">
         <v>-2.0874</v>

--- a/database/event/2248/event_2248_evp_summary.xlsx
+++ b/database/event/2248/event_2248_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0444</v>
+        <v>8.097099999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8742</v>
+        <v>3.4684</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1594</v>
+        <v>3.0174</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0444</v>
+        <v>8.097099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4192</v>
+        <v>4.1149</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6252</v>
+        <v>3.9822</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2191</v>
+        <v>9.011900000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2302</v>
+        <v>4.6858</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6252</v>
+        <v>3.9822</v>
       </c>
       <c r="K2" t="n">
         <v>145</v>
@@ -529,7 +529,7 @@
         <v>95</v>
       </c>
       <c r="M2" t="n">
-        <v>8.855399999999999</v>
+        <v>8.668000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>240</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3505</v>
+        <v>6.3877</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1486</v>
+        <v>2.7362</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4845</v>
+        <v>2.2457</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3505</v>
+        <v>6.3877</v>
       </c>
       <c r="F3" t="n">
-        <v>4.269</v>
+        <v>3.8332</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0815</v>
+        <v>2.5545</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6148</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7404</v>
+        <v>4.1698</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0815</v>
+        <v>2.5545</v>
       </c>
       <c r="K3" t="n">
         <v>145</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8219</v>
+        <v>6.7243</v>
       </c>
       <c r="N3" t="n">
         <v>240</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3916</v>
+        <v>5.4482</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7379</v>
+        <v>2.3338</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1025</v>
+        <v>1.8216</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3916</v>
+        <v>5.4482</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1525</v>
+        <v>3.5375</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2391</v>
+        <v>1.9107</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1525</v>
+        <v>6.9777</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3657</v>
+        <v>3.6281</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2391</v>
+        <v>1.9107</v>
       </c>
       <c r="K4" t="n">
         <v>145</v>
@@ -621,7 +621,7 @@
         <v>95</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6048</v>
+        <v>5.5388</v>
       </c>
       <c r="N4" t="n">
         <v>240</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3767</v>
+        <v>3.2234</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4464</v>
+        <v>1.3808</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9014</v>
+        <v>0.8172</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3767</v>
+        <v>3.2234</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3416</v>
+        <v>3.861</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9649</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9068</v>
+        <v>8.1174</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9771</v>
+        <v>4.2207</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9649</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>108</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0122</v>
+        <v>3.5831</v>
       </c>
       <c r="N5" t="n">
         <v>157</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8053</v>
+        <v>2.9952</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2017</v>
+        <v>1.283</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6737</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8053</v>
+        <v>2.9952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8562</v>
+        <v>2.2736</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9491</v>
+        <v>0.7216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8562</v>
+        <v>2.5245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.694</v>
+        <v>1.3126</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9491</v>
+        <v>0.7216</v>
       </c>
       <c r="K6" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L6" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6431</v>
+        <v>2.0342</v>
       </c>
       <c r="N6" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5357</v>
+        <v>2.9314</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0862</v>
+        <v>1.2557</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5663</v>
+        <v>0.6854</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5357</v>
+        <v>2.9314</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4537</v>
+        <v>2.7828</v>
       </c>
       <c r="G7" t="n">
-        <v>0.082</v>
+        <v>0.1486</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4537</v>
+        <v>4.3185</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9888</v>
+        <v>2.2454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.082</v>
+        <v>0.1486</v>
       </c>
       <c r="K7" t="n">
         <v>108</v>
@@ -759,7 +759,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0708</v>
+        <v>2.394</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -768,173 +768,173 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.0791</v>
+        <v>2.8839</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8905999999999999</v>
+        <v>1.2353</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3844</v>
+        <v>0.6639</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0791</v>
+        <v>2.8839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7294</v>
+        <v>1.4394</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3497</v>
+        <v>1.4445</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7294</v>
+        <v>1.4394</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.7484</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3497</v>
+        <v>1.4445</v>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="L8" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9409</v>
+        <v>2.1929</v>
       </c>
       <c r="N8" t="n">
-        <v>153</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9948</v>
+        <v>2.8767</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8545</v>
+        <v>1.2322</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3508</v>
+        <v>0.6607</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9948</v>
+        <v>2.8767</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2861</v>
+        <v>1.4622</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7087</v>
+        <v>1.4145</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2861</v>
+        <v>1.4622</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0424</v>
+        <v>0.7603</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7087</v>
+        <v>1.4145</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7511</v>
+        <v>2.1748</v>
       </c>
       <c r="N9" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8029</v>
+        <v>2.712</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7723</v>
+        <v>1.1617</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2744</v>
+        <v>0.5863</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8029</v>
+        <v>2.712</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5867</v>
+        <v>1.268</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3896</v>
+        <v>1.444</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5867</v>
+        <v>1.268</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4755</v>
+        <v>0.6593</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3896</v>
+        <v>1.444</v>
       </c>
       <c r="K10" t="n">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9141</v>
+        <v>2.1033</v>
       </c>
       <c r="N10" t="n">
-        <v>240</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7907</v>
+        <v>2.1224</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7671</v>
+        <v>0.9091</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2695</v>
+        <v>0.3201</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7907</v>
+        <v>2.1224</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4826</v>
+        <v>-0.0127</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3081</v>
+        <v>2.1351</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4826</v>
+        <v>-0.0127</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3912</v>
+        <v>-0.0066</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3081</v>
+        <v>2.1351</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>95</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6993</v>
+        <v>2.1285</v>
       </c>
       <c r="N11" t="n">
         <v>240</v>
@@ -952,127 +952,127 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4814</v>
+        <v>2.0624</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.8834</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1463</v>
+        <v>0.2931</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4814</v>
+        <v>2.0624</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9386</v>
+        <v>2.0204</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4572</v>
+        <v>0.042</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9386</v>
+        <v>2.0204</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5713</v>
+        <v>1.0505</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4572</v>
+        <v>0.042</v>
       </c>
       <c r="K12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1141</v>
+        <v>1.0925</v>
       </c>
       <c r="N12" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3299</v>
+        <v>2.0451</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5697</v>
+        <v>0.876</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0859</v>
+        <v>0.2852</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3299</v>
+        <v>2.0451</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7246</v>
+        <v>2.3865</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.3414</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7246</v>
+        <v>2.9224</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5873</v>
+        <v>1.5195</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.3414</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1926</v>
+        <v>1.1781</v>
       </c>
       <c r="N13" t="n">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2455</v>
+        <v>1.8751</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5335</v>
+        <v>0.8032</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0523</v>
+        <v>0.2085</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2455</v>
+        <v>1.8751</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3991</v>
+        <v>1.2491</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1536</v>
+        <v>0.626</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3991</v>
+        <v>1.2491</v>
       </c>
       <c r="I14" t="n">
-        <v>1.134</v>
+        <v>0.6495</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1536</v>
+        <v>0.626</v>
       </c>
       <c r="K14" t="n">
         <v>56</v>
@@ -1081,7 +1081,7 @@
         <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9803999999999999</v>
+        <v>1.2755</v>
       </c>
       <c r="N14" t="n">
         <v>153</v>
@@ -1090,170 +1090,170 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2194</v>
+        <v>1.7527</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5223</v>
+        <v>0.7508</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0419</v>
+        <v>0.1532</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2194</v>
+        <v>1.7527</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3436</v>
+        <v>1.7527</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3436</v>
+        <v>1.7527</v>
       </c>
       <c r="I15" t="n">
-        <v>1.089</v>
+        <v>1.7527</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1242</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L15" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9648</v>
+        <v>1.7527</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1804</v>
+        <v>1.7505</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5056</v>
+        <v>0.7498</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0264</v>
+        <v>0.1522</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1804</v>
+        <v>1.7505</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1804</v>
+        <v>2.0948</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.3443</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1804</v>
+        <v>2.0948</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1804</v>
+        <v>1.0892</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.3443</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1804</v>
+        <v>0.7448999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>SEMPHIS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0671</v>
+        <v>1.7475</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4571</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0188</v>
+        <v>0.1509</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0671</v>
+        <v>1.7475</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0671</v>
+        <v>2.1923</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.4448</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0671</v>
+        <v>2.2379</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0671</v>
+        <v>1.1636</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4448</v>
       </c>
       <c r="K17" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0671</v>
+        <v>0.7188</v>
       </c>
       <c r="N17" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4159</v>
+        <v>0.72</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0571</v>
+        <v>0.1208</v>
       </c>
       <c r="E18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="F18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="I18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.971</v>
+        <v>1.6808</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1274,737 +1274,737 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4076</v>
+        <v>0.7168</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0648</v>
+        <v>0.1174</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9515</v>
+        <v>1.6734</v>
       </c>
       <c r="N19" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3909</v>
+        <v>0.5548</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0804</v>
+        <v>-0.0533</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9125</v>
+        <v>1.2952</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.2723</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3698</v>
+        <v>0.545</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0999</v>
+        <v>-0.0636</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.2723</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.8367</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.5644</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.8367</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.5644</v>
       </c>
       <c r="K21" t="n">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.3905999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1938</v>
+        <v>0.5077</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2636</v>
+        <v>-0.1029</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4525</v>
+        <v>1.1853</v>
       </c>
       <c r="N22" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4194</v>
+        <v>1.0764</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1797</v>
+        <v>0.4611</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2768</v>
+        <v>-0.1521</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4194</v>
+        <v>1.0764</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2356</v>
+        <v>1.0764</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8162</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2356</v>
+        <v>1.0764</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0015</v>
+        <v>1.0764</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8162</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1853</v>
+        <v>1.0764</v>
       </c>
       <c r="N23" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4017</v>
+        <v>0.9802</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1721</v>
+        <v>0.4199</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2839</v>
+        <v>-0.1955</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4017</v>
+        <v>0.9802</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4017</v>
+        <v>0.9866</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4017</v>
+        <v>0.9866</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4017</v>
+        <v>0.513</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4017</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3499</v>
+        <v>0.8879</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1499</v>
+        <v>0.3803</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3045</v>
+        <v>-0.2372</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3499</v>
+        <v>0.8879</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5833</v>
+        <v>0.8879</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5833</v>
+        <v>0.8879</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4728</v>
+        <v>0.8879</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2394</v>
+        <v>0.8879</v>
       </c>
       <c r="N25" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1139</v>
+        <v>0.3674</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.338</v>
+        <v>-0.2508</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2658</v>
+        <v>0.8577</v>
       </c>
       <c r="N26" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEMPHIS</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2525</v>
+        <v>0.5907</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1082</v>
+        <v>0.253</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3433</v>
+        <v>-0.3713</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2525</v>
+        <v>0.5907</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9766</v>
+        <v>0.5907</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9766</v>
+        <v>0.5907</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7916</v>
+        <v>0.5907</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="L27" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0675</v>
+        <v>0.5907</v>
       </c>
       <c r="N27" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0066</v>
+        <v>0.0644</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4501</v>
+        <v>-0.5702</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0155</v>
+        <v>0.1503</v>
       </c>
       <c r="N28" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0465</v>
+        <v>0.0635</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4871</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1085</v>
+        <v>0.1483</v>
       </c>
       <c r="N29" t="n">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5104</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1668</v>
+        <v>0.0188</v>
       </c>
       <c r="N30" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8105</v>
+        <v>-0.3476</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3472</v>
+        <v>-0.1489</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7668</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8105</v>
+        <v>-0.3476</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8105</v>
+        <v>0.1719</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8105</v>
+        <v>0.1719</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8105</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="K31" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8105</v>
+        <v>-0.4301</v>
       </c>
       <c r="N31" t="n">
-        <v>74</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8365</v>
+        <v>-0.5199</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3583</v>
+        <v>-0.2227</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7772</v>
+        <v>-0.8727</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8365</v>
+        <v>-0.5199</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8365</v>
+        <v>0.1039</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6238</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8365</v>
+        <v>0.1039</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8365</v>
+        <v>0.054</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6238</v>
       </c>
       <c r="K32" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8365</v>
+        <v>-0.5698</v>
       </c>
       <c r="N32" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8567</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.367</v>
+        <v>-0.2407</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7852</v>
+        <v>-0.8917</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8567</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0074</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8641</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0074</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.006</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8641</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="L33" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8581</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9724</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4165</v>
+        <v>-0.2472</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8313</v>
+        <v>-0.8985</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9724</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2165</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7559</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2165</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1755</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7559</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="L34" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9314</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>157</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4475</v>
+        <v>-0.3101</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8601</v>
+        <v>-0.9649</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0446</v>
+        <v>-0.724</v>
       </c>
       <c r="N35" t="n">
         <v>74</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5002</v>
+        <v>-0.3423</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9091</v>
+        <v>-0.9987</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1677</v>
+        <v>-0.799</v>
       </c>
       <c r="N36" t="n">
         <v>77</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5158</v>
+        <v>-0.3656</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9237</v>
+        <v>-1.0233</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2042</v>
+        <v>-0.8534</v>
       </c>
       <c r="N37" t="n">
         <v>74</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5467</v>
+        <v>-0.3714</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9524</v>
+        <v>-1.0294</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2764</v>
+        <v>-0.867</v>
       </c>
       <c r="N38" t="n">
         <v>77</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5566</v>
+        <v>-0.4359</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9616</v>
+        <v>-1.0974</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2993</v>
+        <v>-1.0176</v>
       </c>
       <c r="N39" t="n">
         <v>74</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8857</v>
+        <v>-0.708</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2677</v>
+        <v>-1.3842</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0677</v>
+        <v>-1.6529</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0874</v>
+        <v>-2.2783</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8941</v>
+        <v>-0.9759</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2755</v>
+        <v>-1.6666</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0874</v>
+        <v>-2.2783</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2459</v>
+        <v>-1.7067</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8415</v>
+        <v>-0.5716</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2459</v>
+        <v>-1.7067</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0098</v>
+        <v>-0.8874</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8415</v>
+        <v>-0.5716</v>
       </c>
       <c r="K41" t="n">
         <v>59</v>
@@ -2323,7 +2323,7 @@
         <v>47</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8513</v>
+        <v>-1.459</v>
       </c>
       <c r="N41" t="n">
         <v>106</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3877</v>
+        <v>1.2465</v>
       </c>
       <c r="J2" t="n">
-        <v>37.4679</v>
+        <v>33.6555</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1899</v>
+        <v>1.117</v>
       </c>
       <c r="J3" t="n">
-        <v>32.1273</v>
+        <v>30.159</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3712</v>
+        <v>-0.2995</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.0224</v>
+        <v>-8.086499999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4011</v>
+        <v>-0.33</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.8297</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6422</v>
+        <v>-0.5827</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.3394</v>
+        <v>-15.7329</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.37</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>16.4268</v>
+        <v>19.8828</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.039</v>
+        <v>0.0375</v>
       </c>
       <c r="J8" t="n">
-        <v>1.053</v>
+        <v>1.0125</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8657</v>
+        <v>-0.9747</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2619</v>
+        <v>-0.1564</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.0713</v>
+        <v>-4.2228</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4265</v>
+        <v>-0.269</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.5155</v>
+        <v>-7.263</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4947</v>
+        <v>1.3385</v>
       </c>
       <c r="J12" t="n">
-        <v>31.3887</v>
+        <v>28.1085</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1831</v>
+        <v>1.153</v>
       </c>
       <c r="J13" t="n">
-        <v>24.8451</v>
+        <v>24.213</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1406</v>
+        <v>1.1297</v>
       </c>
       <c r="J14" t="n">
-        <v>23.9526</v>
+        <v>23.7237</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7694</v>
+        <v>0.894</v>
       </c>
       <c r="J15" t="n">
-        <v>16.1574</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.27</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5501</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>11.5521</v>
+        <v>14.0679</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.82</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1825</v>
+        <v>-0.1661</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.8325</v>
+        <v>-3.4881</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2615</v>
+        <v>-0.2201</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.4915</v>
+        <v>-4.6221</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.64</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4879</v>
+        <v>-0.345</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.2459</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6427</v>
+        <v>-0.4371</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.4967</v>
+        <v>-9.1791</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.49</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.484</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.9352</v>
+        <v>-10.164</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.73</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5364</v>
+        <v>1.0899</v>
       </c>
       <c r="J22" t="n">
-        <v>29.1916</v>
+        <v>20.7081</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.57</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2305</v>
+        <v>0.9042</v>
       </c>
       <c r="J23" t="n">
-        <v>23.3795</v>
+        <v>17.1798</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.39</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8182</v>
+        <v>0.6905</v>
       </c>
       <c r="J24" t="n">
-        <v>15.5458</v>
+        <v>13.1195</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.35</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7307</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>13.8833</v>
+        <v>12.1524</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.33</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6869</v>
+        <v>0.6136</v>
       </c>
       <c r="J26" t="n">
-        <v>13.0511</v>
+        <v>11.6584</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5331</v>
+        <v>0.5249</v>
       </c>
       <c r="J27" t="n">
-        <v>10.1289</v>
+        <v>9.973100000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2583</v>
+        <v>-0.2186</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.9077</v>
+        <v>-4.1534</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.66</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4369</v>
+        <v>-0.327</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.3011</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.39</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8388</v>
+        <v>-0.5774</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.9372</v>
+        <v>-10.9706</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.054</v>
+        <v>-0.7478</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.026</v>
+        <v>-14.2082</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9919</v>
+        <v>0.7125</v>
       </c>
       <c r="J32" t="n">
-        <v>29.757</v>
+        <v>21.375</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6682</v>
+        <v>0.5138</v>
       </c>
       <c r="J33" t="n">
-        <v>20.046</v>
+        <v>15.414</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5658</v>
+        <v>0.4542</v>
       </c>
       <c r="J34" t="n">
-        <v>16.974</v>
+        <v>13.626</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2121</v>
+        <v>-0.1511</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.363</v>
+        <v>-4.533</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.68</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9726</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-29.178</v>
+        <v>-28.353</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3403</v>
+        <v>0.3672</v>
       </c>
       <c r="J37" t="n">
-        <v>10.209</v>
+        <v>11.016</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1756</v>
+        <v>0.1967</v>
       </c>
       <c r="J38" t="n">
-        <v>5.268</v>
+        <v>5.901</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1147</v>
+        <v>0.1326</v>
       </c>
       <c r="J39" t="n">
-        <v>3.441</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0891</v>
+        <v>0.1102</v>
       </c>
       <c r="J40" t="n">
-        <v>2.673</v>
+        <v>3.306</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.319</v>
+        <v>-0.1925</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.57</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.77</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2109</v>
+        <v>-0.1905</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.7962</v>
+        <v>-3.429</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.72</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2878</v>
+        <v>-0.2458</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.1804</v>
+        <v>-4.4244</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.54</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5952</v>
+        <v>-0.4207</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.7136</v>
+        <v>-7.5726</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.45</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7338</v>
+        <v>-0.5047</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.2084</v>
+        <v>-9.0846</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.33</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.895</v>
+        <v>-0.6206</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.11</v>
+        <v>-11.1708</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.98</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8214</v>
+        <v>1.3384</v>
       </c>
       <c r="J47" t="n">
-        <v>32.7852</v>
+        <v>24.0912</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.97</v>
       </c>
       <c r="I48" t="n">
-        <v>1.8122</v>
+        <v>1.3276</v>
       </c>
       <c r="J48" t="n">
-        <v>32.6196</v>
+        <v>23.8968</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.72</v>
       </c>
       <c r="I49" t="n">
-        <v>1.4398</v>
+        <v>1.0548</v>
       </c>
       <c r="J49" t="n">
-        <v>25.9164</v>
+        <v>18.9864</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8169</v>
+        <v>0.7089</v>
       </c>
       <c r="J50" t="n">
-        <v>14.7042</v>
+        <v>12.7602</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2812</v>
+        <v>0.37</v>
       </c>
       <c r="J51" t="n">
-        <v>5.0616</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6616</v>
+        <v>0.6142</v>
       </c>
       <c r="J52" t="n">
-        <v>19.1864</v>
+        <v>17.8118</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0824</v>
+        <v>-0.0597</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.3896</v>
+        <v>-1.7313</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2463</v>
+        <v>-0.1509</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.1427</v>
+        <v>-4.3761</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2463</v>
+        <v>-0.1509</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.1427</v>
+        <v>-4.3761</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5763</v>
+        <v>-0.378</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.7127</v>
+        <v>-10.962</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9393</v>
+        <v>0.6807</v>
       </c>
       <c r="J57" t="n">
-        <v>27.2397</v>
+        <v>19.7403</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6586</v>
+        <v>0.5105</v>
       </c>
       <c r="J58" t="n">
-        <v>19.0994</v>
+        <v>14.8045</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.21</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6334</v>
+        <v>0.4959</v>
       </c>
       <c r="J59" t="n">
-        <v>18.3686</v>
+        <v>14.3811</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1366</v>
+        <v>0.1771</v>
       </c>
       <c r="J60" t="n">
-        <v>3.9614</v>
+        <v>5.1359</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9981</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.9449</v>
+        <v>-28.2257</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.8</v>
       </c>
       <c r="I62" t="n">
-        <v>1.7289</v>
+        <v>1.4796</v>
       </c>
       <c r="J62" t="n">
-        <v>39.7647</v>
+        <v>34.0308</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3818</v>
+        <v>1.2521</v>
       </c>
       <c r="J63" t="n">
-        <v>31.7814</v>
+        <v>28.7983</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6217</v>
+        <v>0.7039</v>
       </c>
       <c r="J64" t="n">
-        <v>14.2991</v>
+        <v>16.1897</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3736</v>
+        <v>0.463</v>
       </c>
       <c r="J65" t="n">
-        <v>8.5928</v>
+        <v>10.649</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9119</v>
+        <v>-0.8756</v>
       </c>
       <c r="J66" t="n">
-        <v>-20.9737</v>
+        <v>-20.1388</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6012</v>
+        <v>0.7461</v>
       </c>
       <c r="J67" t="n">
-        <v>13.8276</v>
+        <v>17.1603</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2726</v>
+        <v>-0.2212</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.2698</v>
+        <v>-5.0876</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.53</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6732</v>
+        <v>-0.455</v>
       </c>
       <c r="J69" t="n">
-        <v>-15.4836</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7125</v>
+        <v>-0.4831</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.3875</v>
+        <v>-11.1113</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.43</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8012</v>
+        <v>-0.5485</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.4276</v>
+        <v>-12.6155</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0646</v>
+        <v>1.0494</v>
       </c>
       <c r="J72" t="n">
-        <v>28.7442</v>
+        <v>28.3338</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8881</v>
       </c>
       <c r="J73" t="n">
-        <v>23.4198</v>
+        <v>23.9787</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6016</v>
+        <v>0.6662</v>
       </c>
       <c r="J74" t="n">
-        <v>16.2432</v>
+        <v>17.9874</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I75" t="n">
-        <v>0.497</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>13.419</v>
+        <v>15.4467</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2058</v>
+        <v>0.286</v>
       </c>
       <c r="J76" t="n">
-        <v>5.5566</v>
+        <v>7.722</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2591</v>
+        <v>0.2708</v>
       </c>
       <c r="J77" t="n">
-        <v>6.9957</v>
+        <v>7.3116</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1037</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.7999</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1478</v>
+        <v>-0.104</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.9906</v>
+        <v>-2.808</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.9343</v>
+        <v>-5.643</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3464</v>
+        <v>-0.2191</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.3528</v>
+        <v>-5.9157</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.517</v>
+        <v>0.4456</v>
       </c>
       <c r="J82" t="n">
-        <v>14.476</v>
+        <v>12.4768</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5041</v>
+        <v>0.4339</v>
       </c>
       <c r="J83" t="n">
-        <v>14.1148</v>
+        <v>12.1492</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.2</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3376</v>
+        <v>0.2889</v>
       </c>
       <c r="J84" t="n">
-        <v>9.4528</v>
+        <v>8.0892</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.95</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1742</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.8776</v>
+        <v>-2.5032</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3376</v>
+        <v>-0.2021</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.4528</v>
+        <v>-5.6588</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3188</v>
+        <v>0.281</v>
       </c>
       <c r="J87" t="n">
-        <v>8.926399999999999</v>
+        <v>7.868</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1668</v>
+        <v>0.1482</v>
       </c>
       <c r="J88" t="n">
-        <v>4.6704</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1668</v>
+        <v>0.1482</v>
       </c>
       <c r="J89" t="n">
-        <v>4.6704</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0668</v>
+        <v>-0.0257</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.8704</v>
+        <v>-0.7196</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1146</v>
+        <v>-0.0557</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.2088</v>
+        <v>-1.5596</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.85</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1692</v>
+        <v>-0.1513</v>
       </c>
       <c r="J92" t="n">
-        <v>-3.7224</v>
+        <v>-3.3286</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2836</v>
+        <v>-0.2249</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.2392</v>
+        <v>-4.9478</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4151</v>
+        <v>-0.2906</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.132199999999999</v>
+        <v>-6.3932</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.466</v>
+        <v>-0.3181</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.252</v>
+        <v>-6.9982</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.4022</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.1626</v>
+        <v>-8.8484</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5404</v>
+        <v>1.3695</v>
       </c>
       <c r="J97" t="n">
-        <v>33.8888</v>
+        <v>30.129</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.67</v>
       </c>
       <c r="I98" t="n">
-        <v>1.4104</v>
+        <v>1.2894</v>
       </c>
       <c r="J98" t="n">
-        <v>31.0288</v>
+        <v>28.3668</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.57</v>
       </c>
       <c r="I99" t="n">
-        <v>1.2129</v>
+        <v>1.174</v>
       </c>
       <c r="J99" t="n">
-        <v>26.6838</v>
+        <v>25.828</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.29</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5875</v>
+        <v>0.7117</v>
       </c>
       <c r="J100" t="n">
-        <v>12.925</v>
+        <v>15.6574</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.27</v>
       </c>
       <c r="I101" t="n">
-        <v>0.5433</v>
+        <v>0.6655</v>
       </c>
       <c r="J101" t="n">
-        <v>11.9526</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4121</v>
+        <v>0.4681</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1267</v>
+        <v>12.6387</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1877</v>
+        <v>0.1828</v>
       </c>
       <c r="J103" t="n">
-        <v>5.0679</v>
+        <v>4.9356</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1485</v>
+        <v>0.1356</v>
       </c>
       <c r="J104" t="n">
-        <v>4.0095</v>
+        <v>3.6612</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3772</v>
+        <v>-0.2393</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.1844</v>
+        <v>-6.4611</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7421</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.0367</v>
+        <v>-13.5675</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.181</v>
+        <v>1.11</v>
       </c>
       <c r="J107" t="n">
-        <v>31.887</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.836</v>
+        <v>0.8187</v>
       </c>
       <c r="J108" t="n">
-        <v>22.572</v>
+        <v>22.1049</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8129</v>
+        <v>0.795</v>
       </c>
       <c r="J109" t="n">
-        <v>21.9483</v>
+        <v>21.465</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7568</v>
+        <v>-0.7071</v>
       </c>
       <c r="J110" t="n">
-        <v>-20.4336</v>
+        <v>-19.0917</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7568</v>
+        <v>-0.7071</v>
       </c>
       <c r="J111" t="n">
-        <v>-20.4336</v>
+        <v>-19.0917</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0318</v>
+        <v>-0.0549</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.795</v>
+        <v>-1.3725</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1561</v>
+        <v>-0.1382</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.9025</v>
+        <v>-3.455</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3096</v>
+        <v>-0.2311</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.74</v>
+        <v>-5.7775</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5429</v>
+        <v>-0.3619</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.5725</v>
+        <v>-9.047499999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.59</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6112</v>
+        <v>-0.4087</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.28</v>
+        <v>-10.2175</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.67</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4855</v>
+        <v>1.3201</v>
       </c>
       <c r="J117" t="n">
-        <v>37.1375</v>
+        <v>33.0025</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.48</v>
       </c>
       <c r="I118" t="n">
-        <v>1.115</v>
+        <v>1.089</v>
       </c>
       <c r="J118" t="n">
-        <v>27.875</v>
+        <v>27.225</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7088</v>
+        <v>0.79</v>
       </c>
       <c r="J119" t="n">
-        <v>17.72</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.23</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6066</v>
       </c>
       <c r="J120" t="n">
-        <v>12.84</v>
+        <v>15.165</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2234</v>
+        <v>-0.1359</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.585</v>
+        <v>-3.3975</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5353</v>
+        <v>0.6344</v>
       </c>
       <c r="J122" t="n">
-        <v>12.8472</v>
+        <v>15.2256</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.1456</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3524</v>
+        <v>-0.2305</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.457599999999999</v>
+        <v>-5.532</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4577</v>
+        <v>-0.2984</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.9848</v>
+        <v>-7.1616</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6947</v>
+        <v>-0.4671</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.6728</v>
+        <v>-11.2104</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.76</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6889</v>
+        <v>1.4511</v>
       </c>
       <c r="J127" t="n">
-        <v>40.5336</v>
+        <v>34.8264</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.48</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1582</v>
+        <v>1.1051</v>
       </c>
       <c r="J128" t="n">
-        <v>27.7968</v>
+        <v>26.5224</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.34</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8571</v>
+        <v>0.8714</v>
       </c>
       <c r="J129" t="n">
-        <v>20.5704</v>
+        <v>20.9136</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.462</v>
+        <v>-0.386</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.088</v>
+        <v>-9.263999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.75</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.8125</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.5272</v>
+        <v>-19.5</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.74</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2828</v>
+        <v>-0.2389</v>
       </c>
       <c r="J132" t="n">
-        <v>-5.656</v>
+        <v>-4.778</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.392</v>
+        <v>-0.3102</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.84</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5221</v>
+        <v>-0.3743</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.442</v>
+        <v>-7.486</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5221</v>
+        <v>-0.3743</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.442</v>
+        <v>-7.486</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7901</v>
+        <v>-0.542</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.802</v>
+        <v>-10.84</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.92</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8428</v>
+        <v>1.5661</v>
       </c>
       <c r="J137" t="n">
-        <v>36.856</v>
+        <v>31.322</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.85</v>
       </c>
       <c r="I138" t="n">
-        <v>1.7235</v>
+        <v>1.4882</v>
       </c>
       <c r="J138" t="n">
-        <v>34.47</v>
+        <v>29.764</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.75</v>
       </c>
       <c r="I139" t="n">
-        <v>1.5454</v>
+        <v>1.3758</v>
       </c>
       <c r="J139" t="n">
-        <v>30.908</v>
+        <v>27.516</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1816</v>
+        <v>0.2838</v>
       </c>
       <c r="J140" t="n">
-        <v>3.632</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0176</v>
+        <v>0.1096</v>
       </c>
       <c r="J141" t="n">
-        <v>0.352</v>
+        <v>2.192</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4789</v>
+        <v>0.5577</v>
       </c>
       <c r="J142" t="n">
-        <v>12.4514</v>
+        <v>14.5002</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.6826</v>
+        <v>-3.0056</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1995</v>
+        <v>-0.1266</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.187</v>
+        <v>-3.2916</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3496</v>
+        <v>-0.2203</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.089600000000001</v>
+        <v>-5.7278</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4087</v>
+        <v>-0.2601</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.6262</v>
+        <v>-6.7626</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8894</v>
+        <v>0.888</v>
       </c>
       <c r="J147" t="n">
-        <v>23.1244</v>
+        <v>23.088</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8669</v>
+        <v>0.8653</v>
       </c>
       <c r="J148" t="n">
-        <v>22.5394</v>
+        <v>22.4978</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.442</v>
+        <v>0.4895</v>
       </c>
       <c r="J149" t="n">
-        <v>11.492</v>
+        <v>12.727</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2413</v>
+        <v>0.3048</v>
       </c>
       <c r="J150" t="n">
-        <v>6.2738</v>
+        <v>7.9248</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0609</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.5834</v>
+        <v>0.2288</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.571</v>
+        <v>0.6877</v>
       </c>
       <c r="J152" t="n">
-        <v>17.13</v>
+        <v>20.631</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4264</v>
+        <v>0.4983</v>
       </c>
       <c r="J153" t="n">
-        <v>12.792</v>
+        <v>14.949</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2786</v>
+        <v>0.3154</v>
       </c>
       <c r="J154" t="n">
-        <v>8.358000000000001</v>
+        <v>9.462</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4204</v>
+        <v>-0.2635</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.612</v>
+        <v>-7.905</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.54</v>
+        <v>-0.35</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.2</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7224</v>
+        <v>0.6838</v>
       </c>
       <c r="J157" t="n">
-        <v>21.672</v>
+        <v>20.514</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3436</v>
+        <v>0.3098</v>
       </c>
       <c r="J158" t="n">
-        <v>10.308</v>
+        <v>9.294</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2444</v>
+        <v>0.2205</v>
       </c>
       <c r="J159" t="n">
-        <v>7.332</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3532</v>
+        <v>-0.2992</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.596</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5251</v>
+        <v>-0.4706</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.753</v>
+        <v>-14.118</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8489</v>
+        <v>0.8357</v>
       </c>
       <c r="J162" t="n">
-        <v>24.6181</v>
+        <v>24.2353</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.826</v>
+        <v>0.8122</v>
       </c>
       <c r="J163" t="n">
-        <v>23.954</v>
+        <v>23.5538</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6579</v>
+        <v>0.6452</v>
       </c>
       <c r="J164" t="n">
-        <v>19.0791</v>
+        <v>18.7108</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.97</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2384</v>
+        <v>-0.1665</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.9136</v>
+        <v>-4.8285</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4847</v>
+        <v>-0.4168</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.0563</v>
+        <v>-12.0872</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1701</v>
+        <v>0.1608</v>
       </c>
       <c r="J167" t="n">
-        <v>4.9329</v>
+        <v>4.6632</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1291</v>
+        <v>0.1116</v>
       </c>
       <c r="J168" t="n">
-        <v>3.7439</v>
+        <v>3.2364</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>0.011</v>
+        <v>-0.0124</v>
       </c>
       <c r="J169" t="n">
-        <v>0.319</v>
+        <v>-0.3596</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2985</v>
+        <v>-0.1884</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.656499999999999</v>
+        <v>-5.4636</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5429</v>
+        <v>-0.3546</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.7441</v>
+        <v>-10.2834</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5723</v>
+        <v>0.6891</v>
       </c>
       <c r="J172" t="n">
-        <v>16.0244</v>
+        <v>19.2948</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5597</v>
+        <v>0.6723</v>
       </c>
       <c r="J173" t="n">
-        <v>15.6716</v>
+        <v>18.8244</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1677</v>
+        <v>-0.0919</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.6956</v>
+        <v>-2.5732</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2042</v>
+        <v>-0.1156</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.7176</v>
+        <v>-3.2368</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.4054</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.2032</v>
+        <v>-11.3512</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2632</v>
+        <v>1.1653</v>
       </c>
       <c r="J177" t="n">
-        <v>35.3696</v>
+        <v>32.6284</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.951</v>
+        <v>0.9425</v>
       </c>
       <c r="J178" t="n">
-        <v>26.628</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1068</v>
+        <v>-0.0379</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.9904</v>
+        <v>-1.0612</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2456</v>
+        <v>-0.1712</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.8768</v>
+        <v>-4.7936</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3139</v>
+        <v>-0.2397</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.789199999999999</v>
+        <v>-6.7116</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8985</v>
+        <v>0.8853</v>
       </c>
       <c r="J182" t="n">
-        <v>25.158</v>
+        <v>24.7884</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.2</v>
       </c>
       <c r="I183" t="n">
-        <v>0.586</v>
+        <v>0.5739</v>
       </c>
       <c r="J183" t="n">
-        <v>16.408</v>
+        <v>16.0692</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5324</v>
+        <v>0.5241</v>
       </c>
       <c r="J184" t="n">
-        <v>14.9072</v>
+        <v>14.6748</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0954</v>
+        <v>-0.0312</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.6712</v>
+        <v>-0.8736</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3039</v>
+        <v>-0.2328</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.5092</v>
+        <v>-6.5184</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4218</v>
+        <v>0.485</v>
       </c>
       <c r="J187" t="n">
-        <v>11.8104</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3934</v>
+        <v>0.4481</v>
       </c>
       <c r="J188" t="n">
-        <v>11.0152</v>
+        <v>12.5468</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.88</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2526</v>
+        <v>-0.153</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.0728</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3621</v>
+        <v>-0.2257</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.1388</v>
+        <v>-6.3196</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4477</v>
+        <v>-0.285</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.5356</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2536</v>
+        <v>1.174</v>
       </c>
       <c r="J192" t="n">
-        <v>27.5792</v>
+        <v>25.828</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.45</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0488</v>
+        <v>1.0504</v>
       </c>
       <c r="J193" t="n">
-        <v>23.0736</v>
+        <v>23.1088</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.33</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7558</v>
+        <v>0.8324</v>
       </c>
       <c r="J194" t="n">
-        <v>16.6276</v>
+        <v>18.3128</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.24</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5351</v>
+        <v>0.6291</v>
       </c>
       <c r="J195" t="n">
-        <v>11.7722</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.14</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2872</v>
+        <v>0.3792</v>
       </c>
       <c r="J196" t="n">
-        <v>6.3184</v>
+        <v>8.3424</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0354</v>
+        <v>-0.0568</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.7788</v>
+        <v>-1.2496</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2618</v>
+        <v>-0.2028</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.7596</v>
+        <v>-4.4616</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2791</v>
+        <v>-0.2127</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.1402</v>
+        <v>-4.6794</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3159</v>
+        <v>-0.2319</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.9498</v>
+        <v>-5.1018</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.53</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6913</v>
+        <v>-0.4658</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.2086</v>
+        <v>-10.2476</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.62</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4379</v>
+        <v>1.2833</v>
       </c>
       <c r="J202" t="n">
-        <v>40.2612</v>
+        <v>35.9324</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.49</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1844</v>
+        <v>1.1204</v>
       </c>
       <c r="J203" t="n">
-        <v>33.1632</v>
+        <v>31.3712</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.08</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1616</v>
+        <v>0.2362</v>
       </c>
       <c r="J204" t="n">
-        <v>4.5248</v>
+        <v>6.6136</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.03</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0013</v>
+        <v>0.0756</v>
       </c>
       <c r="J205" t="n">
-        <v>0.0364</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.96</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3073</v>
+        <v>-0.226</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.6044</v>
+        <v>-6.328</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0612</v>
+        <v>0.0175</v>
       </c>
       <c r="J207" t="n">
-        <v>1.7136</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.91</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1024</v>
+        <v>-0.0992</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.8672</v>
+        <v>-2.7776</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.8</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2993</v>
+        <v>-0.2155</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.3804</v>
+        <v>-6.034</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3424</v>
+        <v>-0.2341</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.587199999999999</v>
+        <v>-6.5548</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7219</v>
+        <v>-0.4879</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.2132</v>
+        <v>-13.6612</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2248/event_2248_evp_summary.xlsx
+++ b/database/event/2248/event_2248_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.097099999999999</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4684</v>
+        <v>3.5129</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0174</v>
+        <v>3.1091</v>
       </c>
       <c r="E2" t="n">
-        <v>8.097099999999999</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1149</v>
+        <v>4.0432</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9822</v>
+        <v>4.1578</v>
       </c>
       <c r="H2" t="n">
-        <v>9.011900000000001</v>
+        <v>8.4459</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6858</v>
+        <v>4.5607</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9822</v>
+        <v>4.1578</v>
       </c>
       <c r="K2" t="n">
         <v>145</v>
@@ -529,7 +529,7 @@
         <v>95</v>
       </c>
       <c r="M2" t="n">
-        <v>8.668000000000001</v>
+        <v>8.718499999999999</v>
       </c>
       <c r="N2" t="n">
         <v>240</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3877</v>
+        <v>6.5529</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7362</v>
+        <v>2.807</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2457</v>
+        <v>2.3588</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3877</v>
+        <v>6.5529</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8332</v>
+        <v>3.7432</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5545</v>
+        <v>2.8097</v>
       </c>
       <c r="H3" t="n">
-        <v>8.019600000000001</v>
+        <v>7.456</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1698</v>
+        <v>4.0262</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5545</v>
+        <v>2.8097</v>
       </c>
       <c r="K3" t="n">
         <v>145</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7243</v>
+        <v>6.835900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>240</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4482</v>
+        <v>5.6003</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3338</v>
+        <v>2.3989</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8216</v>
+        <v>1.9252</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4482</v>
+        <v>5.6003</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5375</v>
+        <v>3.485</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9107</v>
+        <v>2.1153</v>
       </c>
       <c r="H4" t="n">
-        <v>6.9777</v>
+        <v>6.6042</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6281</v>
+        <v>3.5662</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9107</v>
+        <v>2.1153</v>
       </c>
       <c r="K4" t="n">
         <v>145</v>
@@ -621,7 +621,7 @@
         <v>95</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5388</v>
+        <v>5.6815</v>
       </c>
       <c r="N4" t="n">
         <v>240</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2234</v>
+        <v>3.1651</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3808</v>
+        <v>1.3558</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8172</v>
+        <v>0.8166</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2234</v>
+        <v>3.1651</v>
       </c>
       <c r="F5" t="n">
-        <v>3.861</v>
+        <v>3.7842</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6191</v>
       </c>
       <c r="H5" t="n">
-        <v>8.1174</v>
+        <v>7.5914</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2207</v>
+        <v>4.0993</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6191</v>
       </c>
       <c r="K5" t="n">
         <v>108</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5831</v>
+        <v>3.4802</v>
       </c>
       <c r="N5" t="n">
         <v>157</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9952</v>
+        <v>3.003</v>
       </c>
       <c r="C6" t="n">
-        <v>1.283</v>
+        <v>1.2863</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7428</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9952</v>
+        <v>3.003</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2736</v>
+        <v>1.4902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7216</v>
+        <v>1.5128</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5245</v>
+        <v>1.4902</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3126</v>
+        <v>0.8047</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7216</v>
+        <v>1.5128</v>
       </c>
       <c r="K6" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0342</v>
+        <v>2.3175</v>
       </c>
       <c r="N6" t="n">
-        <v>157</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9314</v>
+        <v>2.9836</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2557</v>
+        <v>1.278</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6854</v>
+        <v>0.734</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9314</v>
+        <v>2.9836</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7828</v>
+        <v>2.2219</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1486</v>
+        <v>0.7617</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3185</v>
+        <v>2.4365</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2454</v>
+        <v>1.3157</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1486</v>
+        <v>0.7617</v>
       </c>
       <c r="K7" t="n">
         <v>108</v>
@@ -759,7 +759,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.394</v>
+        <v>2.0774</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8839</v>
+        <v>2.9634</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2353</v>
+        <v>1.2694</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6639</v>
+        <v>0.7248</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8839</v>
+        <v>2.9634</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4394</v>
+        <v>1.4084</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4445</v>
+        <v>1.555</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4394</v>
+        <v>1.4084</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7484</v>
+        <v>0.7605</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4445</v>
+        <v>1.555</v>
       </c>
       <c r="K8" t="n">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="L8" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1929</v>
+        <v>2.3155</v>
       </c>
       <c r="N8" t="n">
-        <v>240</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8767</v>
+        <v>2.8647</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2322</v>
+        <v>1.2271</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6607</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8767</v>
+        <v>2.8647</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4622</v>
+        <v>2.7168</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4145</v>
+        <v>0.1479</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4622</v>
+        <v>4.0697</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7603</v>
+        <v>2.1976</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4145</v>
+        <v>0.1479</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1748</v>
+        <v>2.3455</v>
       </c>
       <c r="N9" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.712</v>
+        <v>2.6681</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1617</v>
+        <v>1.1429</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5863</v>
+        <v>0.5904</v>
       </c>
       <c r="E10" t="n">
-        <v>2.712</v>
+        <v>2.6681</v>
       </c>
       <c r="F10" t="n">
-        <v>1.268</v>
+        <v>1.1439</v>
       </c>
       <c r="G10" t="n">
-        <v>1.444</v>
+        <v>1.5242</v>
       </c>
       <c r="H10" t="n">
-        <v>1.268</v>
+        <v>1.1439</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6593</v>
+        <v>0.6177</v>
       </c>
       <c r="J10" t="n">
-        <v>1.444</v>
+        <v>1.5242</v>
       </c>
       <c r="K10" t="n">
         <v>56</v>
@@ -897,7 +897,7 @@
         <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1033</v>
+        <v>2.1419</v>
       </c>
       <c r="N10" t="n">
         <v>153</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1224</v>
+        <v>2.4589</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9091</v>
+        <v>1.0533</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3201</v>
+        <v>0.4951</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1224</v>
+        <v>2.4589</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0127</v>
+        <v>0.095</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1351</v>
+        <v>2.3639</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0127</v>
+        <v>0.095</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0066</v>
+        <v>0.0513</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1351</v>
+        <v>2.3639</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>95</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1285</v>
+        <v>2.4152</v>
       </c>
       <c r="N11" t="n">
         <v>240</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0624</v>
+        <v>2.0258</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8834</v>
+        <v>0.8678</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2931</v>
+        <v>0.298</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0624</v>
+        <v>2.0258</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0204</v>
+        <v>1.9119</v>
       </c>
       <c r="G12" t="n">
-        <v>0.042</v>
+        <v>0.1139</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0204</v>
+        <v>1.9119</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0505</v>
+        <v>1.0324</v>
       </c>
       <c r="J12" t="n">
-        <v>0.042</v>
+        <v>0.1139</v>
       </c>
       <c r="K12" t="n">
         <v>56</v>
@@ -989,7 +989,7 @@
         <v>97</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0925</v>
+        <v>1.1463</v>
       </c>
       <c r="N12" t="n">
         <v>153</v>
@@ -998,308 +998,308 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0451</v>
+        <v>1.9275</v>
       </c>
       <c r="C13" t="n">
-        <v>0.876</v>
+        <v>0.8256</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2852</v>
+        <v>0.2532</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0451</v>
+        <v>1.9275</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3865</v>
+        <v>1.2085</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3414</v>
+        <v>0.719</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9224</v>
+        <v>1.2085</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5195</v>
+        <v>0.6526</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3414</v>
+        <v>0.719</v>
       </c>
       <c r="K13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1781</v>
+        <v>1.3716</v>
       </c>
       <c r="N13" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8751</v>
+        <v>1.9009</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8032</v>
+        <v>0.8143</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2085</v>
+        <v>0.2411</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8751</v>
+        <v>1.9009</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2491</v>
+        <v>2.2871</v>
       </c>
       <c r="G14" t="n">
-        <v>0.626</v>
+        <v>-0.3862</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2491</v>
+        <v>2.6519</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6495</v>
+        <v>1.432</v>
       </c>
       <c r="J14" t="n">
-        <v>0.626</v>
+        <v>-0.3862</v>
       </c>
       <c r="K14" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L14" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2755</v>
+        <v>1.0458</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7527</v>
+        <v>1.7773</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7508</v>
+        <v>0.7613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1532</v>
+        <v>0.1849</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7527</v>
+        <v>1.7773</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7527</v>
+        <v>1.9661</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.1888</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7527</v>
+        <v>1.9661</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7527</v>
+        <v>1.0617</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.1888</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7527</v>
+        <v>0.8729000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7505</v>
+        <v>1.6875</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7498</v>
+        <v>0.7228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1522</v>
+        <v>0.144</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7505</v>
+        <v>1.6875</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0948</v>
+        <v>1.6875</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0948</v>
+        <v>1.6875</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0892</v>
+        <v>1.6875</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7448999999999999</v>
+        <v>1.6875</v>
       </c>
       <c r="N16" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEMPHIS</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7475</v>
+        <v>1.5896</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1509</v>
+        <v>0.0994</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7475</v>
+        <v>1.5896</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1923</v>
+        <v>1.5896</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4448</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2379</v>
+        <v>1.5896</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1636</v>
+        <v>1.5896</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4448</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7188</v>
+        <v>1.5896</v>
       </c>
       <c r="N17" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>SEMPHIS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6808</v>
+        <v>1.5804</v>
       </c>
       <c r="C18" t="n">
-        <v>0.72</v>
+        <v>0.677</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1208</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6808</v>
+        <v>1.5804</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6808</v>
+        <v>2.0206</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.4402</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6808</v>
+        <v>2.0206</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6808</v>
+        <v>1.0911</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.4402</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6808</v>
+        <v>0.6509</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7168</v>
+        <v>0.6768</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1174</v>
+        <v>0.095</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6734</v>
+        <v>1.5799</v>
       </c>
       <c r="N19" t="n">
         <v>128</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5548</v>
+        <v>0.5426</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0533</v>
+        <v>-0.0475</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2952</v>
+        <v>1.2668</v>
       </c>
       <c r="N20" t="n">
         <v>127</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2723</v>
+        <v>1.1282</v>
       </c>
       <c r="C21" t="n">
-        <v>0.545</v>
+        <v>0.4833</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0636</v>
+        <v>-0.1106</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2723</v>
+        <v>1.1282</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8367</v>
+        <v>1.7163</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5644</v>
+        <v>-0.5881</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8367</v>
+        <v>1.7163</v>
       </c>
       <c r="I21" t="n">
-        <v>0.955</v>
+        <v>0.9268</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5644</v>
+        <v>-0.5881</v>
       </c>
       <c r="K21" t="n">
         <v>59</v>
@@ -1403,7 +1403,7 @@
         <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3905999999999999</v>
+        <v>0.3387</v>
       </c>
       <c r="N21" t="n">
         <v>106</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5077</v>
+        <v>0.4745</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1029</v>
+        <v>-0.1199</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1853</v>
+        <v>1.1078</v>
       </c>
       <c r="N22" t="n">
         <v>77</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4611</v>
+        <v>0.4355</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1521</v>
+        <v>-0.1614</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0764</v>
+        <v>1.0166</v>
       </c>
       <c r="N23" t="n">
         <v>127</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9802</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4199</v>
+        <v>0.3988</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1955</v>
+        <v>-0.2004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9802</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9866</v>
+        <v>0.8741</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0064</v>
+        <v>0.0568</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9866</v>
+        <v>0.8741</v>
       </c>
       <c r="I24" t="n">
-        <v>0.513</v>
+        <v>0.472</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0064</v>
+        <v>0.0568</v>
       </c>
       <c r="K24" t="n">
         <v>59</v>
@@ -1541,7 +1541,7 @@
         <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>106</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3803</v>
+        <v>0.3641</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2372</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8879</v>
+        <v>0.8501</v>
       </c>
       <c r="N25" t="n">
         <v>127</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3674</v>
+        <v>0.3237</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2508</v>
+        <v>-0.2801</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8577</v>
+        <v>0.7558</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="C27" t="n">
-        <v>0.253</v>
+        <v>0.2187</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3713</v>
+        <v>-0.3918</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5907</v>
+        <v>0.5105</v>
       </c>
       <c r="N27" t="n">
         <v>127</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0644</v>
+        <v>0.0429</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5702</v>
+        <v>-0.5786</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1503</v>
+        <v>0.1002</v>
       </c>
       <c r="N28" t="n">
         <v>77</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0635</v>
+        <v>0.0377</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5841</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1483</v>
+        <v>0.0881</v>
       </c>
       <c r="N29" t="n">
         <v>74</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0081</v>
+        <v>-0.0264</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.6522</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0188</v>
+        <v>-0.0616</v>
       </c>
       <c r="N30" t="n">
         <v>127</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3476</v>
+        <v>-0.353</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1512</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.7849</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3476</v>
+        <v>-0.353</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1719</v>
+        <v>0.1996</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5195</v>
+        <v>-0.5526</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1719</v>
+        <v>0.1996</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1078</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5195</v>
+        <v>-0.5526</v>
       </c>
       <c r="K31" t="n">
         <v>108</v>
@@ -1863,7 +1863,7 @@
         <v>49</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4301</v>
+        <v>-0.4448</v>
       </c>
       <c r="N31" t="n">
         <v>157</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5199</v>
+        <v>-0.5443</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2227</v>
+        <v>-0.2332</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8727</v>
+        <v>-0.872</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5199</v>
+        <v>-0.5443</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1039</v>
+        <v>0.1183</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6238</v>
+        <v>-0.6626</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1039</v>
+        <v>0.1183</v>
       </c>
       <c r="I32" t="n">
-        <v>0.054</v>
+        <v>0.0639</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6238</v>
+        <v>-0.6626</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5698</v>
+        <v>-0.5987</v>
       </c>
       <c r="N32" t="n">
         <v>106</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2407</v>
+        <v>-0.2588</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8917</v>
+        <v>-0.8992</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="N33" t="n">
         <v>77</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2472</v>
+        <v>-0.2707</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8985</v>
+        <v>-0.9119</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6319</v>
       </c>
       <c r="N34" t="n">
         <v>74</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3101</v>
+        <v>-0.3327</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9649</v>
+        <v>-0.9778</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.724</v>
+        <v>-0.7768</v>
       </c>
       <c r="N35" t="n">
         <v>74</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3423</v>
+        <v>-0.3594</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9987</v>
+        <v>-1.0061</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.799</v>
+        <v>-0.839</v>
       </c>
       <c r="N36" t="n">
         <v>77</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3656</v>
+        <v>-0.3865</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0233</v>
+        <v>-1.0349</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8534</v>
+        <v>-0.9023</v>
       </c>
       <c r="N37" t="n">
         <v>74</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3714</v>
+        <v>-0.3908</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0294</v>
+        <v>-1.0395</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.867</v>
+        <v>-0.9123</v>
       </c>
       <c r="N38" t="n">
         <v>77</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4359</v>
+        <v>-0.4544</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0974</v>
+        <v>-1.1071</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0176</v>
+        <v>-1.0607</v>
       </c>
       <c r="N39" t="n">
         <v>74</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.708</v>
+        <v>-0.6849</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3842</v>
+        <v>-1.3521</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6529</v>
+        <v>-1.599</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2783</v>
+        <v>-2.1729</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9759</v>
+        <v>-0.9308</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6666</v>
+        <v>-1.6134</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2783</v>
+        <v>-2.1729</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7067</v>
+        <v>-1.5678</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5716</v>
+        <v>-0.6051</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7067</v>
+        <v>-1.5678</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8874</v>
+        <v>-0.8466</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5716</v>
+        <v>-0.6051</v>
       </c>
       <c r="K41" t="n">
         <v>59</v>
@@ -2323,7 +2323,7 @@
         <v>47</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.459</v>
+        <v>-1.4517</v>
       </c>
       <c r="N41" t="n">
         <v>106</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2465</v>
+        <v>1.2876</v>
       </c>
       <c r="J2" t="n">
-        <v>33.6555</v>
+        <v>34.7652</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.117</v>
+        <v>1.1003</v>
       </c>
       <c r="J3" t="n">
-        <v>30.159</v>
+        <v>29.7081</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2995</v>
+        <v>-0.287</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.086499999999999</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.33</v>
+        <v>-0.3154</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.91</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5827</v>
+        <v>-0.5455</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.7329</v>
+        <v>-14.7285</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.37</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7053</v>
       </c>
       <c r="J7" t="n">
-        <v>19.8828</v>
+        <v>19.0431</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0375</v>
+        <v>0.0432</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0125</v>
+        <v>1.1664</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0361</v>
+        <v>-0.0428</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9747</v>
+        <v>-1.1556</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1564</v>
+        <v>-0.1695</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2228</v>
+        <v>-4.5765</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.269</v>
+        <v>-0.282</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.263</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3385</v>
+        <v>1.4377</v>
       </c>
       <c r="J12" t="n">
-        <v>28.1085</v>
+        <v>30.1917</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1.153</v>
+        <v>1.17</v>
       </c>
       <c r="J13" t="n">
-        <v>24.213</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1297</v>
+        <v>1.1359</v>
       </c>
       <c r="J14" t="n">
-        <v>23.7237</v>
+        <v>23.8539</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.894</v>
+        <v>0.8517</v>
       </c>
       <c r="J15" t="n">
-        <v>18.774</v>
+        <v>17.8857</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.27</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6545</v>
       </c>
       <c r="J16" t="n">
-        <v>14.0679</v>
+        <v>13.7445</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.82</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1661</v>
+        <v>-0.1916</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.4881</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2201</v>
+        <v>-0.2442</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.6221</v>
+        <v>-5.1282</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.64</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.345</v>
+        <v>-0.3649</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.245</v>
+        <v>-7.6629</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4371</v>
+        <v>-0.4524</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.1791</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.49</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.484</v>
+        <v>-0.4964</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.164</v>
+        <v>-10.4244</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.73</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0899</v>
+        <v>1.2047</v>
       </c>
       <c r="J22" t="n">
-        <v>20.7081</v>
+        <v>22.8893</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.57</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9042</v>
+        <v>1.006</v>
       </c>
       <c r="J23" t="n">
-        <v>17.1798</v>
+        <v>19.114</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.39</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6905</v>
+        <v>0.773</v>
       </c>
       <c r="J24" t="n">
-        <v>13.1195</v>
+        <v>14.687</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.35</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="J25" t="n">
-        <v>12.1524</v>
+        <v>13.6249</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.33</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6136</v>
+        <v>0.6884</v>
       </c>
       <c r="J26" t="n">
-        <v>11.6584</v>
+        <v>13.0796</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5249</v>
+        <v>0.5552</v>
       </c>
       <c r="J27" t="n">
-        <v>9.973100000000001</v>
+        <v>10.5488</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2186</v>
+        <v>-0.243</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.1534</v>
+        <v>-4.617</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.66</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.327</v>
+        <v>-0.3476</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.213</v>
+        <v>-6.6044</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.39</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5774</v>
+        <v>-0.5833</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.9706</v>
+        <v>-11.0827</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7478</v>
+        <v>-0.7396</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.2082</v>
+        <v>-14.0524</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7125</v>
+        <v>0.7834</v>
       </c>
       <c r="J32" t="n">
-        <v>21.375</v>
+        <v>23.502</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5138</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>15.414</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4542</v>
+        <v>0.4983</v>
       </c>
       <c r="J34" t="n">
-        <v>13.626</v>
+        <v>14.949</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1511</v>
+        <v>-0.15</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.533</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.68</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.353</v>
+        <v>-26.019</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3672</v>
+        <v>0.3909</v>
       </c>
       <c r="J37" t="n">
-        <v>11.016</v>
+        <v>11.727</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1967</v>
+        <v>0.2065</v>
       </c>
       <c r="J38" t="n">
-        <v>5.901</v>
+        <v>6.195</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1326</v>
+        <v>0.1431</v>
       </c>
       <c r="J39" t="n">
-        <v>3.978</v>
+        <v>4.293</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1102</v>
+        <v>0.1205</v>
       </c>
       <c r="J40" t="n">
-        <v>3.306</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1925</v>
+        <v>-0.205</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.775</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.77</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1905</v>
+        <v>-0.2209</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.429</v>
+        <v>-3.9762</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.72</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2458</v>
+        <v>-0.2737</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.4244</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.54</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4207</v>
+        <v>-0.4398</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.5726</v>
+        <v>-7.9164</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.45</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5047</v>
+        <v>-0.5182</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.0846</v>
+        <v>-9.3276</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.33</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6206</v>
+        <v>-0.6249</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.1708</v>
+        <v>-11.2482</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.98</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3384</v>
+        <v>1.4724</v>
       </c>
       <c r="J47" t="n">
-        <v>24.0912</v>
+        <v>26.5032</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.97</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3276</v>
+        <v>1.461</v>
       </c>
       <c r="J48" t="n">
-        <v>23.8968</v>
+        <v>26.298</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.72</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0548</v>
+        <v>1.1719</v>
       </c>
       <c r="J49" t="n">
-        <v>18.9864</v>
+        <v>21.0942</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7089</v>
+        <v>0.7974</v>
       </c>
       <c r="J50" t="n">
-        <v>12.7602</v>
+        <v>14.3532</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I51" t="n">
-        <v>0.37</v>
+        <v>0.4143</v>
       </c>
       <c r="J51" t="n">
-        <v>6.66</v>
+        <v>7.4574</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6142</v>
+        <v>0.6817</v>
       </c>
       <c r="J52" t="n">
-        <v>17.8118</v>
+        <v>19.7693</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0597</v>
+        <v>-0.0699</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.7313</v>
+        <v>-2.0271</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1509</v>
+        <v>-0.1653</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.3761</v>
+        <v>-4.7937</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1509</v>
+        <v>-0.1653</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.3761</v>
+        <v>-4.7937</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.378</v>
+        <v>-0.3889</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.962</v>
+        <v>-11.2781</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6807</v>
+        <v>0.7497</v>
       </c>
       <c r="J57" t="n">
-        <v>19.7403</v>
+        <v>21.7413</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5105</v>
+        <v>0.5622</v>
       </c>
       <c r="J58" t="n">
-        <v>14.8045</v>
+        <v>16.3038</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.21</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4959</v>
+        <v>0.5458</v>
       </c>
       <c r="J59" t="n">
-        <v>14.3811</v>
+        <v>15.8282</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1771</v>
+        <v>0.1866</v>
       </c>
       <c r="J60" t="n">
-        <v>5.1359</v>
+        <v>5.4114</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.8911</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.2257</v>
+        <v>-25.8419</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.8</v>
       </c>
       <c r="I62" t="n">
-        <v>1.4796</v>
+        <v>1.4685</v>
       </c>
       <c r="J62" t="n">
-        <v>34.0308</v>
+        <v>33.7755</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2521</v>
+        <v>1.2276</v>
       </c>
       <c r="J63" t="n">
-        <v>28.7983</v>
+        <v>28.2348</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7039</v>
+        <v>0.6781</v>
       </c>
       <c r="J64" t="n">
-        <v>16.1897</v>
+        <v>15.5963</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.463</v>
+        <v>0.4626</v>
       </c>
       <c r="J65" t="n">
-        <v>10.649</v>
+        <v>10.6398</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8756</v>
+        <v>-0.798</v>
       </c>
       <c r="J66" t="n">
-        <v>-20.1388</v>
+        <v>-18.354</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7461</v>
+        <v>0.6842</v>
       </c>
       <c r="J67" t="n">
-        <v>17.1603</v>
+        <v>15.7366</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2212</v>
+        <v>-0.243</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.0876</v>
+        <v>-5.589</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.53</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.455</v>
+        <v>-0.4679</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.465</v>
+        <v>-10.7617</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4831</v>
+        <v>-0.4943</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.1113</v>
+        <v>-11.3689</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.43</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5485</v>
+        <v>-0.5553</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.6155</v>
+        <v>-12.7719</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0494</v>
+        <v>1.003</v>
       </c>
       <c r="J72" t="n">
-        <v>28.3338</v>
+        <v>27.081</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8881</v>
+        <v>0.8393</v>
       </c>
       <c r="J73" t="n">
-        <v>23.9787</v>
+        <v>22.6611</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6662</v>
+        <v>0.6428</v>
       </c>
       <c r="J74" t="n">
-        <v>17.9874</v>
+        <v>17.3556</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5587</v>
       </c>
       <c r="J75" t="n">
-        <v>15.4467</v>
+        <v>15.0849</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.286</v>
+        <v>0.2988</v>
       </c>
       <c r="J76" t="n">
-        <v>7.722</v>
+        <v>8.067600000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2708</v>
+        <v>0.2702</v>
       </c>
       <c r="J77" t="n">
-        <v>7.3116</v>
+        <v>7.2954</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.1924</v>
+        <v>-2.5326</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.104</v>
+        <v>-0.1178</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.808</v>
+        <v>-3.1806</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.643</v>
+        <v>-6.0669</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2191</v>
+        <v>-0.2348</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.9157</v>
+        <v>-6.3396</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4456</v>
+        <v>0.4552</v>
       </c>
       <c r="J82" t="n">
-        <v>12.4768</v>
+        <v>12.7456</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4339</v>
+        <v>0.4441</v>
       </c>
       <c r="J83" t="n">
-        <v>12.1492</v>
+        <v>12.4348</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.2</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2889</v>
+        <v>0.3044</v>
       </c>
       <c r="J84" t="n">
-        <v>8.0892</v>
+        <v>8.523199999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.95</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.5032</v>
+        <v>-2.702</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2021</v>
+        <v>-0.2126</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.6588</v>
+        <v>-5.9528</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.281</v>
+        <v>0.2901</v>
       </c>
       <c r="J87" t="n">
-        <v>7.868</v>
+        <v>8.1228</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1482</v>
+        <v>0.1601</v>
       </c>
       <c r="J88" t="n">
-        <v>4.1496</v>
+        <v>4.4828</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1482</v>
+        <v>0.1601</v>
       </c>
       <c r="J89" t="n">
-        <v>4.1496</v>
+        <v>4.4828</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0257</v>
+        <v>-0.0292</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.7196</v>
+        <v>-0.8176</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0557</v>
+        <v>-0.0625</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.5596</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.85</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1513</v>
+        <v>-0.1733</v>
       </c>
       <c r="J92" t="n">
-        <v>-3.3286</v>
+        <v>-3.8126</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2249</v>
+        <v>-0.2459</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.9478</v>
+        <v>-5.4098</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2906</v>
+        <v>-0.3103</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.3932</v>
+        <v>-6.8266</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3181</v>
+        <v>-0.3371</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.9982</v>
+        <v>-7.4162</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4022</v>
+        <v>-0.4175</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.8484</v>
+        <v>-9.185</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3695</v>
+        <v>1.3592</v>
       </c>
       <c r="J97" t="n">
-        <v>30.129</v>
+        <v>29.9024</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.67</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2894</v>
+        <v>1.2739</v>
       </c>
       <c r="J98" t="n">
-        <v>28.3668</v>
+        <v>28.0258</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.57</v>
       </c>
       <c r="I99" t="n">
-        <v>1.174</v>
+        <v>1.1499</v>
       </c>
       <c r="J99" t="n">
-        <v>25.828</v>
+        <v>25.2978</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.29</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7117</v>
+        <v>0.6923</v>
       </c>
       <c r="J100" t="n">
-        <v>15.6574</v>
+        <v>15.2306</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.27</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6655</v>
+        <v>0.6514</v>
       </c>
       <c r="J101" t="n">
-        <v>14.641</v>
+        <v>14.3308</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4681</v>
+        <v>0.4553</v>
       </c>
       <c r="J102" t="n">
-        <v>12.6387</v>
+        <v>12.2931</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1828</v>
+        <v>0.1854</v>
       </c>
       <c r="J103" t="n">
-        <v>4.9356</v>
+        <v>5.0058</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1356</v>
+        <v>0.1387</v>
       </c>
       <c r="J104" t="n">
-        <v>3.6612</v>
+        <v>3.7449</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2393</v>
+        <v>-0.2547</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4611</v>
+        <v>-6.8769</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5082</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.5675</v>
+        <v>-13.7214</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.11</v>
+        <v>1.0662</v>
       </c>
       <c r="J107" t="n">
-        <v>29.97</v>
+        <v>28.7874</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8187</v>
+        <v>0.7704</v>
       </c>
       <c r="J108" t="n">
-        <v>22.1049</v>
+        <v>20.8008</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.795</v>
+        <v>0.7497</v>
       </c>
       <c r="J109" t="n">
-        <v>21.465</v>
+        <v>20.2419</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7071</v>
+        <v>-0.6572</v>
       </c>
       <c r="J110" t="n">
-        <v>-19.0917</v>
+        <v>-17.7444</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7071</v>
+        <v>-0.6572</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.0917</v>
+        <v>-17.7444</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0549</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.3725</v>
+        <v>-1.835</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1382</v>
+        <v>-0.1582</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.455</v>
+        <v>-3.955</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2311</v>
+        <v>-0.2506</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.7775</v>
+        <v>-6.265</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3619</v>
+        <v>-0.378</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.047499999999999</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.59</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4087</v>
+        <v>-0.4226</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.2175</v>
+        <v>-10.565</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.67</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3201</v>
+        <v>1.3008</v>
       </c>
       <c r="J117" t="n">
-        <v>33.0025</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.48</v>
       </c>
       <c r="I118" t="n">
-        <v>1.089</v>
+        <v>1.0523</v>
       </c>
       <c r="J118" t="n">
-        <v>27.225</v>
+        <v>26.3075</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="J119" t="n">
-        <v>19.75</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.23</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6066</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>15.165</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1359</v>
+        <v>-0.1161</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.3975</v>
+        <v>-2.9025</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6344</v>
+        <v>0.6011</v>
       </c>
       <c r="J122" t="n">
-        <v>15.2256</v>
+        <v>14.4264</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.028</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2305</v>
+        <v>-0.2479</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.532</v>
+        <v>-5.9496</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2984</v>
+        <v>-0.3145</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.1616</v>
+        <v>-7.548</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4671</v>
+        <v>-0.476</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.2104</v>
+        <v>-11.424</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.76</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4511</v>
+        <v>1.4354</v>
       </c>
       <c r="J127" t="n">
-        <v>34.8264</v>
+        <v>34.4496</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.48</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1051</v>
+        <v>1.0669</v>
       </c>
       <c r="J128" t="n">
-        <v>26.5224</v>
+        <v>25.6056</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.34</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8714</v>
+        <v>0.8236</v>
       </c>
       <c r="J129" t="n">
-        <v>20.9136</v>
+        <v>19.7664</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.386</v>
+        <v>-0.3614</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.263999999999999</v>
+        <v>-8.6736</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.75</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8125</v>
+        <v>-0.7449</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.5</v>
+        <v>-17.8776</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.74</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2389</v>
+        <v>-0.2646</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.778</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3102</v>
+        <v>-0.3329</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.204</v>
+        <v>-6.658</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3743</v>
+        <v>-0.3943</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.486</v>
+        <v>-7.886</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3743</v>
+        <v>-0.3943</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.486</v>
+        <v>-7.886</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.542</v>
+        <v>-0.5515</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.84</v>
+        <v>-11.03</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.92</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5661</v>
+        <v>1.568</v>
       </c>
       <c r="J137" t="n">
-        <v>31.322</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.85</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4882</v>
+        <v>1.4859</v>
       </c>
       <c r="J138" t="n">
-        <v>29.764</v>
+        <v>29.718</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.75</v>
       </c>
       <c r="I139" t="n">
-        <v>1.3758</v>
+        <v>1.3669</v>
       </c>
       <c r="J139" t="n">
-        <v>27.516</v>
+        <v>27.338</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2838</v>
+        <v>0.3095</v>
       </c>
       <c r="J140" t="n">
-        <v>5.676</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1096</v>
+        <v>0.1475</v>
       </c>
       <c r="J141" t="n">
-        <v>2.192</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5577</v>
+        <v>0.5381</v>
       </c>
       <c r="J142" t="n">
-        <v>14.5002</v>
+        <v>13.9906</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.0056</v>
+        <v>-3.3722</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1266</v>
+        <v>-0.141</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.2916</v>
+        <v>-3.666</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2203</v>
+        <v>-0.2357</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.7278</v>
+        <v>-6.1282</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2601</v>
+        <v>-0.275</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.7626</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.888</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>23.088</v>
+        <v>21.7152</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8653</v>
+        <v>0.8153</v>
       </c>
       <c r="J148" t="n">
-        <v>22.4978</v>
+        <v>21.1978</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4895</v>
+        <v>0.4808</v>
       </c>
       <c r="J149" t="n">
-        <v>12.727</v>
+        <v>12.5008</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3048</v>
+        <v>0.3118</v>
       </c>
       <c r="J150" t="n">
-        <v>7.9248</v>
+        <v>8.1068</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I151" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="J151" t="n">
-        <v>0.2288</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6877</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>20.631</v>
+        <v>19.914</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4983</v>
+        <v>0.4912</v>
       </c>
       <c r="J153" t="n">
-        <v>14.949</v>
+        <v>14.736</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3154</v>
+        <v>0.3205</v>
       </c>
       <c r="J154" t="n">
-        <v>9.462</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2635</v>
+        <v>-0.2756</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.905</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.35</v>
+        <v>-0.3603</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.5</v>
+        <v>-10.809</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6838</v>
+        <v>0.6455</v>
       </c>
       <c r="J157" t="n">
-        <v>20.514</v>
+        <v>19.365</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3098</v>
+        <v>0.3082</v>
       </c>
       <c r="J158" t="n">
-        <v>9.294</v>
+        <v>9.246</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2205</v>
+        <v>0.2246</v>
       </c>
       <c r="J159" t="n">
-        <v>6.615</v>
+        <v>6.738</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2992</v>
+        <v>-0.2939</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.976000000000001</v>
+        <v>-8.817</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4706</v>
+        <v>-0.4509</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.118</v>
+        <v>-13.527</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8357</v>
+        <v>0.7865</v>
       </c>
       <c r="J162" t="n">
-        <v>24.2353</v>
+        <v>22.8085</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8122</v>
+        <v>0.7659</v>
       </c>
       <c r="J163" t="n">
-        <v>23.5538</v>
+        <v>22.2111</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6452</v>
+        <v>0.6186</v>
       </c>
       <c r="J164" t="n">
-        <v>18.7108</v>
+        <v>17.9394</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.97</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1665</v>
+        <v>-0.1607</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.8285</v>
+        <v>-4.6603</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4168</v>
+        <v>-0.3957</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.0872</v>
+        <v>-11.4753</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1608</v>
+        <v>0.1634</v>
       </c>
       <c r="J167" t="n">
-        <v>4.6632</v>
+        <v>4.7386</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1116</v>
+        <v>0.1143</v>
       </c>
       <c r="J168" t="n">
-        <v>3.2364</v>
+        <v>3.3147</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0124</v>
+        <v>-0.019</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.3596</v>
+        <v>-0.551</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1884</v>
+        <v>-0.2042</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.4636</v>
+        <v>-5.9218</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3546</v>
+        <v>-0.3673</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.2834</v>
+        <v>-10.6517</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6891</v>
+        <v>0.6649</v>
       </c>
       <c r="J172" t="n">
-        <v>19.2948</v>
+        <v>18.6172</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6723</v>
+        <v>0.6496</v>
       </c>
       <c r="J173" t="n">
-        <v>18.8244</v>
+        <v>18.1888</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0919</v>
+        <v>-0.1019</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.5732</v>
+        <v>-2.8532</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1156</v>
+        <v>-0.1266</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.2368</v>
+        <v>-3.5448</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4054</v>
+        <v>-0.4138</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.3512</v>
+        <v>-11.5864</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1653</v>
+        <v>1.1277</v>
       </c>
       <c r="J177" t="n">
-        <v>32.6284</v>
+        <v>31.5756</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9425</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>26.39</v>
+        <v>24.7128</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0379</v>
+        <v>-0.0261</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.0612</v>
+        <v>-0.7308</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1712</v>
+        <v>-0.164</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.7936</v>
+        <v>-4.592</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2397</v>
+        <v>-0.2297</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.7116</v>
+        <v>-6.4316</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8853</v>
+        <v>0.8293</v>
       </c>
       <c r="J182" t="n">
-        <v>24.7884</v>
+        <v>23.2204</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.2</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5739</v>
+        <v>0.5546</v>
       </c>
       <c r="J183" t="n">
-        <v>16.0692</v>
+        <v>15.5288</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5241</v>
+        <v>0.5098</v>
       </c>
       <c r="J184" t="n">
-        <v>14.6748</v>
+        <v>14.2744</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0312</v>
+        <v>-0.0214</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.8736</v>
+        <v>-0.5992</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2328</v>
+        <v>-0.225</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.5184</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.485</v>
+        <v>0.4747</v>
       </c>
       <c r="J187" t="n">
-        <v>13.58</v>
+        <v>13.2916</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4481</v>
+        <v>0.4406</v>
       </c>
       <c r="J188" t="n">
-        <v>12.5468</v>
+        <v>12.3368</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.88</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.153</v>
+        <v>-0.1668</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.284</v>
+        <v>-4.6704</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2257</v>
+        <v>-0.2399</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.3196</v>
+        <v>-6.7172</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.285</v>
+        <v>-0.2984</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.98</v>
+        <v>-8.3552</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.174</v>
+        <v>1.145</v>
       </c>
       <c r="J192" t="n">
-        <v>25.828</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.45</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0504</v>
+        <v>1.007</v>
       </c>
       <c r="J193" t="n">
-        <v>23.1088</v>
+        <v>22.154</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.33</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8324</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>18.3128</v>
+        <v>17.4416</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.24</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6291</v>
+        <v>0.6126</v>
       </c>
       <c r="J195" t="n">
-        <v>13.8402</v>
+        <v>13.4772</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.14</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3792</v>
+        <v>0.3878</v>
       </c>
       <c r="J196" t="n">
-        <v>8.3424</v>
+        <v>8.531599999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0568</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.2496</v>
+        <v>-1.6478</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2028</v>
+        <v>-0.2223</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.4616</v>
+        <v>-4.8906</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2127</v>
+        <v>-0.2322</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.6794</v>
+        <v>-5.1084</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2319</v>
+        <v>-0.2512</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.1018</v>
+        <v>-5.5264</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.53</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4658</v>
+        <v>-0.4764</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.2476</v>
+        <v>-10.4808</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.62</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2833</v>
+        <v>1.2574</v>
       </c>
       <c r="J202" t="n">
-        <v>35.9324</v>
+        <v>35.2072</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.49</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1204</v>
+        <v>1.0831</v>
       </c>
       <c r="J203" t="n">
-        <v>31.3712</v>
+        <v>30.3268</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.08</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2362</v>
+        <v>0.2507</v>
       </c>
       <c r="J204" t="n">
-        <v>6.6136</v>
+        <v>7.0196</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.03</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0756</v>
+        <v>0.098</v>
       </c>
       <c r="J205" t="n">
-        <v>2.1168</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.96</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.226</v>
+        <v>-0.2116</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.328</v>
+        <v>-5.9248</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0175</v>
+        <v>-0.0019</v>
       </c>
       <c r="J207" t="n">
-        <v>0.49</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.91</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0992</v>
+        <v>-0.1171</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.7776</v>
+        <v>-3.2788</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.8</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2155</v>
+        <v>-0.2342</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.034</v>
+        <v>-6.5576</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2341</v>
+        <v>-0.2528</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.5548</v>
+        <v>-7.0784</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4879</v>
+        <v>-0.4967</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.6612</v>
+        <v>-13.9076</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2248/event_2248_evp_summary.xlsx
+++ b/database/event/2248/event_2248_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.201000000000001</v>
+        <v>8.0411</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5129</v>
+        <v>3.4444</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1091</v>
+        <v>3.0573</v>
       </c>
       <c r="E2" t="n">
-        <v>8.201000000000001</v>
+        <v>8.0411</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0432</v>
+        <v>3.88</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1578</v>
+        <v>4.1611</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4459</v>
+        <v>8.1244</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5607</v>
+        <v>4.5616</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1578</v>
+        <v>4.1611</v>
       </c>
       <c r="K2" t="n">
         <v>145</v>
@@ -529,7 +529,7 @@
         <v>95</v>
       </c>
       <c r="M2" t="n">
-        <v>8.718499999999999</v>
+        <v>8.7227</v>
       </c>
       <c r="N2" t="n">
         <v>240</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5529</v>
+        <v>6.5131</v>
       </c>
       <c r="C3" t="n">
-        <v>2.807</v>
+        <v>2.7899</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3588</v>
+        <v>2.3612</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5529</v>
+        <v>6.5131</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7432</v>
+        <v>3.6388</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8097</v>
+        <v>2.8743</v>
       </c>
       <c r="H3" t="n">
-        <v>7.456</v>
+        <v>7.2191</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0262</v>
+        <v>4.0533</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8097</v>
+        <v>2.8743</v>
       </c>
       <c r="K3" t="n">
         <v>145</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>6.835900000000001</v>
+        <v>6.9276</v>
       </c>
       <c r="N3" t="n">
         <v>240</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6003</v>
+        <v>5.5437</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3989</v>
+        <v>2.3747</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9252</v>
+        <v>1.9196</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6003</v>
+        <v>5.5437</v>
       </c>
       <c r="F4" t="n">
-        <v>3.485</v>
+        <v>3.4051</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1153</v>
+        <v>2.1386</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6042</v>
+        <v>6.3416</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5662</v>
+        <v>3.5606</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1153</v>
+        <v>2.1386</v>
       </c>
       <c r="K4" t="n">
         <v>145</v>
@@ -621,7 +621,7 @@
         <v>95</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6815</v>
+        <v>5.699199999999999</v>
       </c>
       <c r="N4" t="n">
         <v>240</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1651</v>
+        <v>2.9566</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3558</v>
+        <v>1.2665</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8166</v>
+        <v>0.7411</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1651</v>
+        <v>2.9566</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7842</v>
+        <v>3.6441</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6191</v>
+        <v>-0.6875</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5914</v>
+        <v>7.2389</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0993</v>
+        <v>4.0644</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6191</v>
+        <v>-0.6875</v>
       </c>
       <c r="K5" t="n">
         <v>108</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4802</v>
+        <v>3.3769</v>
       </c>
       <c r="N5" t="n">
         <v>157</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.003</v>
+        <v>2.8874</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2863</v>
+        <v>1.2368</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7428</v>
+        <v>0.7096</v>
       </c>
       <c r="E6" t="n">
-        <v>3.003</v>
+        <v>2.8874</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4902</v>
+        <v>1.3858</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5128</v>
+        <v>1.5016</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4902</v>
+        <v>1.3858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8047</v>
+        <v>0.7781</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5128</v>
+        <v>1.5016</v>
       </c>
       <c r="K6" t="n">
         <v>145</v>
@@ -713,7 +713,7 @@
         <v>95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3175</v>
+        <v>2.2797</v>
       </c>
       <c r="N6" t="n">
         <v>240</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9836</v>
+        <v>2.8793</v>
       </c>
       <c r="C7" t="n">
-        <v>1.278</v>
+        <v>1.2334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.734</v>
+        <v>0.7059</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9836</v>
+        <v>2.8793</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2219</v>
+        <v>2.1517</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7617</v>
+        <v>0.7276</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4365</v>
+        <v>2.1517</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3157</v>
+        <v>1.2081</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7617</v>
+        <v>0.7276</v>
       </c>
       <c r="K7" t="n">
         <v>108</v>
@@ -759,7 +759,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0774</v>
+        <v>1.9357</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9634</v>
+        <v>2.8461</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2694</v>
+        <v>1.2191</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7248</v>
+        <v>0.6907</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9634</v>
+        <v>2.8461</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4084</v>
+        <v>2.7397</v>
       </c>
       <c r="G8" t="n">
-        <v>1.555</v>
+        <v>0.1064</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4084</v>
+        <v>3.8435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7605</v>
+        <v>2.158</v>
       </c>
       <c r="J8" t="n">
-        <v>1.555</v>
+        <v>0.1064</v>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L8" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3155</v>
+        <v>2.2644</v>
       </c>
       <c r="N8" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8647</v>
+        <v>2.7894</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2271</v>
+        <v>1.1948</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6649</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8647</v>
+        <v>2.7894</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7168</v>
+        <v>1.2323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1479</v>
+        <v>1.5571</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0697</v>
+        <v>1.2323</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1976</v>
+        <v>0.6919</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1479</v>
+        <v>1.5571</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3455</v>
+        <v>2.249</v>
       </c>
       <c r="N9" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6681</v>
+        <v>2.5653</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1429</v>
+        <v>1.0989</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5904</v>
+        <v>0.5628</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6681</v>
+        <v>2.5653</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1439</v>
+        <v>1.1174</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5242</v>
+        <v>1.4479</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1439</v>
+        <v>1.1174</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6177</v>
+        <v>0.6274</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5242</v>
+        <v>1.4479</v>
       </c>
       <c r="K10" t="n">
         <v>56</v>
@@ -897,7 +897,7 @@
         <v>97</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1419</v>
+        <v>2.0753</v>
       </c>
       <c r="N10" t="n">
         <v>153</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4589</v>
+        <v>2.5006</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0533</v>
+        <v>1.0711</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4951</v>
+        <v>0.5334</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4589</v>
+        <v>2.5006</v>
       </c>
       <c r="F11" t="n">
-        <v>0.095</v>
+        <v>0.0794</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3639</v>
+        <v>2.4212</v>
       </c>
       <c r="H11" t="n">
-        <v>0.095</v>
+        <v>0.0794</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0513</v>
+        <v>0.0446</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3639</v>
+        <v>2.4212</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>95</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4152</v>
+        <v>2.4658</v>
       </c>
       <c r="N11" t="n">
         <v>240</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0258</v>
+        <v>2.0631</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8678</v>
+        <v>0.8837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.298</v>
+        <v>0.3341</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0258</v>
+        <v>2.0631</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9119</v>
+        <v>1.936</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1139</v>
+        <v>0.1271</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9119</v>
+        <v>1.936</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0324</v>
+        <v>1.087</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1139</v>
+        <v>0.1271</v>
       </c>
       <c r="K12" t="n">
         <v>56</v>
@@ -989,7 +989,7 @@
         <v>97</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1463</v>
+        <v>1.2141</v>
       </c>
       <c r="N12" t="n">
         <v>153</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9275</v>
+        <v>2.016</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8256</v>
+        <v>0.8636</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2532</v>
+        <v>0.3126</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9275</v>
+        <v>2.016</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2085</v>
+        <v>2.3651</v>
       </c>
       <c r="G13" t="n">
-        <v>0.719</v>
+        <v>-0.3491</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2085</v>
+        <v>2.437</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6526</v>
+        <v>1.3683</v>
       </c>
       <c r="J13" t="n">
-        <v>0.719</v>
+        <v>-0.3491</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3716</v>
+        <v>1.0192</v>
       </c>
       <c r="N13" t="n">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9009</v>
+        <v>1.7925</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8143</v>
+        <v>0.7678</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2411</v>
+        <v>0.2108</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9009</v>
+        <v>1.7925</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2871</v>
+        <v>1.0588</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3862</v>
+        <v>0.7337</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6519</v>
+        <v>1.0588</v>
       </c>
       <c r="I14" t="n">
-        <v>1.432</v>
+        <v>0.5945</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3862</v>
+        <v>0.7337</v>
       </c>
       <c r="K14" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L14" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0458</v>
+        <v>1.3282</v>
       </c>
       <c r="N14" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7773</v>
+        <v>1.7763</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7613</v>
+        <v>0.7609</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1849</v>
+        <v>0.2034</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7773</v>
+        <v>1.7763</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9661</v>
+        <v>1.9178</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1888</v>
+        <v>-0.1415</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9661</v>
+        <v>1.9178</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0617</v>
+        <v>1.0768</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1888</v>
+        <v>-0.1415</v>
       </c>
       <c r="K15" t="n">
         <v>56</v>
@@ -1127,7 +1127,7 @@
         <v>97</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8729000000000001</v>
+        <v>0.9353</v>
       </c>
       <c r="N15" t="n">
         <v>153</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7228</v>
+        <v>0.7153</v>
       </c>
       <c r="D16" t="n">
-        <v>0.144</v>
+        <v>0.1549</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6875</v>
+        <v>1.6698</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1182,32 +1182,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6784</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0994</v>
+        <v>0.1157</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5896</v>
+        <v>1.5838</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEMPHIS</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5804</v>
+        <v>1.567</v>
       </c>
       <c r="C18" t="n">
-        <v>0.677</v>
+        <v>0.6712</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1081</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5804</v>
+        <v>1.567</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0206</v>
+        <v>1.567</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4402</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0206</v>
+        <v>1.567</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0911</v>
+        <v>1.567</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4402</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6509</v>
+        <v>1.567</v>
       </c>
       <c r="N18" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>SEMPHIS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5799</v>
+        <v>1.5056</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6768</v>
+        <v>0.6449</v>
       </c>
       <c r="D19" t="n">
-        <v>0.095</v>
+        <v>0.0801</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5799</v>
+        <v>1.5056</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5799</v>
+        <v>1.9871</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.4815</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5799</v>
+        <v>1.9871</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5799</v>
+        <v>1.1157</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.4815</v>
       </c>
       <c r="K19" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5799</v>
+        <v>0.6341999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5426</v>
+        <v>0.4707</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0475</v>
+        <v>-0.1052</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2668</v>
+        <v>1.0988</v>
       </c>
       <c r="N20" t="n">
         <v>127</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1282</v>
+        <v>1.0076</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4833</v>
+        <v>0.4316</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1106</v>
+        <v>-0.1468</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1282</v>
+        <v>1.0076</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7163</v>
+        <v>1.0076</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5881</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7163</v>
+        <v>1.0076</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9268</v>
+        <v>1.0076</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5881</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3387</v>
+        <v>1.0076</v>
       </c>
       <c r="N21" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4745</v>
+        <v>0.4061</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1199</v>
+        <v>-0.1739</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1078</v>
+        <v>0.948</v>
       </c>
       <c r="N22" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0166</v>
+        <v>0.9414</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4355</v>
+        <v>0.4033</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1614</v>
+        <v>-0.1769</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0166</v>
+        <v>0.9414</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0166</v>
+        <v>1.5167</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.5753</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0166</v>
+        <v>1.5167</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0166</v>
+        <v>0.8516</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.5753</v>
       </c>
       <c r="K23" t="n">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0166</v>
+        <v>0.2763</v>
       </c>
       <c r="N23" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8749</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3988</v>
+        <v>0.3748</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2004</v>
+        <v>-0.2072</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8749</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8741</v>
+        <v>0.8629</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0568</v>
+        <v>0.012</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8741</v>
+        <v>0.8629</v>
       </c>
       <c r="I24" t="n">
-        <v>0.472</v>
+        <v>0.4845</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0568</v>
+        <v>0.012</v>
       </c>
       <c r="K24" t="n">
         <v>59</v>
@@ -1541,7 +1541,7 @@
         <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.4965</v>
       </c>
       <c r="N24" t="n">
         <v>106</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3641</v>
+        <v>0.3371</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2372</v>
+        <v>-0.2473</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8501</v>
+        <v>0.787</v>
       </c>
       <c r="N25" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3237</v>
+        <v>0.3139</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2801</v>
+        <v>-0.272</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7558</v>
+        <v>0.7328</v>
       </c>
       <c r="N26" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2187</v>
+        <v>0.2056</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3918</v>
+        <v>-0.3871</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5105</v>
+        <v>0.48</v>
       </c>
       <c r="N27" t="n">
         <v>127</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0429</v>
+        <v>0.0233</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5786</v>
+        <v>-0.581</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1002</v>
+        <v>0.0545</v>
       </c>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0377</v>
+        <v>0.0231</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5841</v>
+        <v>-0.5812</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0881</v>
+        <v>0.0539</v>
       </c>
       <c r="N29" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0264</v>
+        <v>0.0026</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6522</v>
+        <v>-0.6031</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0616</v>
+        <v>0.006</v>
       </c>
       <c r="N30" t="n">
         <v>127</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.353</v>
+        <v>-0.3559</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1512</v>
+        <v>-0.1525</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7849</v>
+        <v>-0.7679</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.353</v>
+        <v>-0.3559</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1996</v>
+        <v>0.1651</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5526</v>
+        <v>-0.521</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1996</v>
+        <v>0.1651</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1078</v>
+        <v>0.0927</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5526</v>
+        <v>-0.521</v>
       </c>
       <c r="K31" t="n">
         <v>108</v>
@@ -1863,7 +1863,7 @@
         <v>49</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4448</v>
+        <v>-0.4283</v>
       </c>
       <c r="N31" t="n">
         <v>157</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5443</v>
+        <v>-0.5301</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2332</v>
+        <v>-0.2271</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.872</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5443</v>
+        <v>-0.5301</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1183</v>
+        <v>0.1076</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6626</v>
+        <v>-0.6377</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1183</v>
+        <v>0.1076</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0639</v>
+        <v>0.0604</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6626</v>
+        <v>-0.6377</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5987</v>
+        <v>-0.5773</v>
       </c>
       <c r="N32" t="n">
         <v>106</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2588</v>
+        <v>-0.2391</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8992</v>
+        <v>-0.8601</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6042</v>
+        <v>-0.5583</v>
       </c>
       <c r="N33" t="n">
         <v>77</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2707</v>
+        <v>-0.2559</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9119</v>
+        <v>-0.8779</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6319</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>74</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3327</v>
+        <v>-0.3142</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9778</v>
+        <v>-0.9399</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7768</v>
+        <v>-0.7335</v>
       </c>
       <c r="N35" t="n">
         <v>74</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3594</v>
+        <v>-0.3405</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0061</v>
+        <v>-0.9679</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.839</v>
+        <v>-0.7948</v>
       </c>
       <c r="N36" t="n">
         <v>77</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3865</v>
+        <v>-0.3721</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0349</v>
+        <v>-1.0015</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9023</v>
+        <v>-0.8686</v>
       </c>
       <c r="N37" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3908</v>
+        <v>-0.3725</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0395</v>
+        <v>-1.0019</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9123</v>
+        <v>-0.8696</v>
       </c>
       <c r="N38" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4544</v>
+        <v>-0.4405</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1071</v>
+        <v>-1.0743</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0607</v>
+        <v>-1.0284</v>
       </c>
       <c r="N39" t="n">
         <v>74</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6849</v>
+        <v>-0.6549</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3521</v>
+        <v>-1.3022</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.599</v>
+        <v>-1.5288</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1729</v>
+        <v>-1.9362</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9308</v>
+        <v>-0.8294</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6134</v>
+        <v>-1.4878</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1729</v>
+        <v>-1.9362</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5678</v>
+        <v>-1.3559</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6051</v>
+        <v>-0.5803</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5678</v>
+        <v>-1.3559</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8466</v>
+        <v>-0.7613</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6051</v>
+        <v>-0.5803</v>
       </c>
       <c r="K41" t="n">
         <v>59</v>
@@ -2323,7 +2323,7 @@
         <v>47</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4517</v>
+        <v>-1.3416</v>
       </c>
       <c r="N41" t="n">
         <v>106</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2876</v>
+        <v>1.3162</v>
       </c>
       <c r="J2" t="n">
-        <v>34.7652</v>
+        <v>35.5374</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1003</v>
+        <v>1.1034</v>
       </c>
       <c r="J3" t="n">
-        <v>29.7081</v>
+        <v>29.7918</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.287</v>
+        <v>-0.2469</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.749</v>
+        <v>-6.6663</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3154</v>
+        <v>-0.2743</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.5158</v>
+        <v>-7.4061</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5455</v>
+        <v>-0.5063</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.7285</v>
+        <v>-13.6701</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.37</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7053</v>
+        <v>0.6491</v>
       </c>
       <c r="J7" t="n">
-        <v>19.0431</v>
+        <v>17.5257</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0432</v>
+        <v>0.0292</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1664</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0428</v>
+        <v>-0.0325</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1556</v>
+        <v>-0.8774999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1695</v>
+        <v>-0.1492</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.5765</v>
+        <v>-4.0284</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.282</v>
+        <v>-0.2632</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.614</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.71</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4377</v>
+        <v>1.475</v>
       </c>
       <c r="J12" t="n">
-        <v>30.1917</v>
+        <v>30.975</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1.17</v>
+        <v>1.1889</v>
       </c>
       <c r="J13" t="n">
-        <v>24.57</v>
+        <v>24.9669</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1359</v>
+        <v>1.1514</v>
       </c>
       <c r="J14" t="n">
-        <v>23.8539</v>
+        <v>24.1794</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8517</v>
+        <v>0.8437</v>
       </c>
       <c r="J15" t="n">
-        <v>17.8857</v>
+        <v>17.7177</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.27</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6545</v>
+        <v>0.6333</v>
       </c>
       <c r="J16" t="n">
-        <v>13.7445</v>
+        <v>13.2993</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.82</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1916</v>
+        <v>-0.1756</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.0236</v>
+        <v>-3.6876</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.77</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2442</v>
+        <v>-0.2301</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.1282</v>
+        <v>-4.8321</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.64</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3649</v>
+        <v>-0.354</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.6629</v>
+        <v>-7.434</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4524</v>
+        <v>-0.4459</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.500400000000001</v>
+        <v>-9.363899999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.49</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4964</v>
+        <v>-0.4941</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.4244</v>
+        <v>-10.3761</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.73</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2047</v>
+        <v>1.2022</v>
       </c>
       <c r="J22" t="n">
-        <v>22.8893</v>
+        <v>22.8418</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.57</v>
       </c>
       <c r="I23" t="n">
-        <v>1.006</v>
+        <v>0.9978</v>
       </c>
       <c r="J23" t="n">
-        <v>19.114</v>
+        <v>18.9582</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.39</v>
       </c>
       <c r="I24" t="n">
-        <v>0.773</v>
+        <v>0.7659</v>
       </c>
       <c r="J24" t="n">
-        <v>14.687</v>
+        <v>14.5521</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.35</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7171</v>
+        <v>0.7111</v>
       </c>
       <c r="J25" t="n">
-        <v>13.6249</v>
+        <v>13.5109</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.33</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6884</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>13.0796</v>
+        <v>12.977</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5552</v>
+        <v>0.5618</v>
       </c>
       <c r="J27" t="n">
-        <v>10.5488</v>
+        <v>10.6742</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.243</v>
+        <v>-0.2289</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.617</v>
+        <v>-4.3491</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.66</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3476</v>
+        <v>-0.3366</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.6044</v>
+        <v>-6.3954</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.39</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5833</v>
+        <v>-0.5925</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.0827</v>
+        <v>-11.2575</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7396</v>
+        <v>-0.7795</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.0524</v>
+        <v>-14.8105</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7834</v>
+        <v>0.7674</v>
       </c>
       <c r="J32" t="n">
-        <v>23.502</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>16.95</v>
+        <v>16.617</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4983</v>
+        <v>0.4788</v>
       </c>
       <c r="J34" t="n">
-        <v>14.949</v>
+        <v>14.364</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.15</v>
+        <v>-0.1191</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.5</v>
+        <v>-3.573</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.68</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8673</v>
+        <v>-0.8504</v>
       </c>
       <c r="J36" t="n">
-        <v>-26.019</v>
+        <v>-25.512</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3909</v>
+        <v>0.3353</v>
       </c>
       <c r="J37" t="n">
-        <v>11.727</v>
+        <v>10.059</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2065</v>
+        <v>0.1658</v>
       </c>
       <c r="J38" t="n">
-        <v>6.195</v>
+        <v>4.974</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1431</v>
+        <v>0.111</v>
       </c>
       <c r="J39" t="n">
-        <v>4.293</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1205</v>
+        <v>0.092</v>
       </c>
       <c r="J40" t="n">
-        <v>3.615</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.205</v>
+        <v>-0.1844</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.15</v>
+        <v>-5.532</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.77</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2209</v>
+        <v>-0.2036</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.9762</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.72</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2737</v>
+        <v>-0.2605</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.9266</v>
+        <v>-4.689</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.54</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4398</v>
+        <v>-0.4348</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.9164</v>
+        <v>-7.8264</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.45</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5182</v>
+        <v>-0.5185</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.3276</v>
+        <v>-9.333</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.33</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6249</v>
+        <v>-0.6399</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.2482</v>
+        <v>-11.5182</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.98</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4724</v>
+        <v>1.4885</v>
       </c>
       <c r="J47" t="n">
-        <v>26.5032</v>
+        <v>26.793</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.97</v>
       </c>
       <c r="I48" t="n">
-        <v>1.461</v>
+        <v>1.4764</v>
       </c>
       <c r="J48" t="n">
-        <v>26.298</v>
+        <v>26.5752</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.72</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1719</v>
+        <v>1.1727</v>
       </c>
       <c r="J49" t="n">
-        <v>21.0942</v>
+        <v>21.1086</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7974</v>
+        <v>0.7933</v>
       </c>
       <c r="J50" t="n">
-        <v>14.3532</v>
+        <v>14.2794</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4143</v>
+        <v>0.3808</v>
       </c>
       <c r="J51" t="n">
-        <v>7.4574</v>
+        <v>6.8544</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6817</v>
+        <v>0.6519</v>
       </c>
       <c r="J52" t="n">
-        <v>19.7693</v>
+        <v>18.9051</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0699</v>
+        <v>-0.0568</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.0271</v>
+        <v>-1.6472</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1653</v>
+        <v>-0.1455</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.7937</v>
+        <v>-4.2195</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1653</v>
+        <v>-0.1455</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.7937</v>
+        <v>-4.2195</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3889</v>
+        <v>-0.3772</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.2781</v>
+        <v>-10.9388</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7497</v>
+        <v>0.7336</v>
       </c>
       <c r="J57" t="n">
-        <v>21.7413</v>
+        <v>21.2744</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5622</v>
+        <v>0.5514</v>
       </c>
       <c r="J58" t="n">
-        <v>16.3038</v>
+        <v>15.9906</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.21</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5458</v>
+        <v>0.5352</v>
       </c>
       <c r="J59" t="n">
-        <v>15.8282</v>
+        <v>15.5208</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1866</v>
+        <v>0.1577</v>
       </c>
       <c r="J60" t="n">
-        <v>5.4114</v>
+        <v>4.5733</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8911</v>
+        <v>-0.8772</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.8419</v>
+        <v>-25.4388</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.8</v>
       </c>
       <c r="I62" t="n">
-        <v>1.4685</v>
+        <v>1.4985</v>
       </c>
       <c r="J62" t="n">
-        <v>33.7755</v>
+        <v>34.4655</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2276</v>
+        <v>1.2437</v>
       </c>
       <c r="J63" t="n">
-        <v>28.2348</v>
+        <v>28.6051</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.27</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6781</v>
+        <v>0.6534</v>
       </c>
       <c r="J64" t="n">
-        <v>15.5963</v>
+        <v>15.0282</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4626</v>
+        <v>0.4314</v>
       </c>
       <c r="J65" t="n">
-        <v>10.6398</v>
+        <v>9.9222</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.798</v>
+        <v>-0.781</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.354</v>
+        <v>-17.963</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.27</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6842</v>
+        <v>0.6632</v>
       </c>
       <c r="J67" t="n">
-        <v>15.7366</v>
+        <v>15.2536</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.243</v>
+        <v>-0.2283</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.589</v>
+        <v>-5.2509</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.53</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4679</v>
+        <v>-0.4627</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.7617</v>
+        <v>-10.6421</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4943</v>
+        <v>-0.4919</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.3689</v>
+        <v>-11.3137</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.43</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5553</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.7719</v>
+        <v>-12.903</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>1.003</v>
+        <v>1.0019</v>
       </c>
       <c r="J72" t="n">
-        <v>27.081</v>
+        <v>27.0513</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.35</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8393</v>
+        <v>0.8203</v>
       </c>
       <c r="J73" t="n">
-        <v>22.6611</v>
+        <v>22.1481</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6428</v>
+        <v>0.6146</v>
       </c>
       <c r="J74" t="n">
-        <v>17.3556</v>
+        <v>16.5942</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5587</v>
+        <v>0.5282</v>
       </c>
       <c r="J75" t="n">
-        <v>15.0849</v>
+        <v>14.2614</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2988</v>
+        <v>0.2672</v>
       </c>
       <c r="J76" t="n">
-        <v>8.067600000000001</v>
+        <v>7.2144</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2702</v>
+        <v>0.2222</v>
       </c>
       <c r="J77" t="n">
-        <v>7.2954</v>
+        <v>5.9994</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.5326</v>
+        <v>-2.1357</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1178</v>
+        <v>-0.1012</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.1806</v>
+        <v>-2.7324</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.0669</v>
+        <v>-5.5269</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2348</v>
+        <v>-0.2148</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.3396</v>
+        <v>-5.7996</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4552</v>
+        <v>0.3889</v>
       </c>
       <c r="J82" t="n">
-        <v>12.7456</v>
+        <v>10.8892</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.32</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4441</v>
+        <v>0.3783</v>
       </c>
       <c r="J83" t="n">
-        <v>12.4348</v>
+        <v>10.5924</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.2</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3044</v>
+        <v>0.2497</v>
       </c>
       <c r="J84" t="n">
-        <v>8.523199999999999</v>
+        <v>6.9916</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.95</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0965</v>
+        <v>-0.0796</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.702</v>
+        <v>-2.2288</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2126</v>
+        <v>-0.1924</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.9528</v>
+        <v>-5.3872</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2901</v>
+        <v>0.2779</v>
       </c>
       <c r="J87" t="n">
-        <v>8.1228</v>
+        <v>7.7812</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1601</v>
+        <v>0.1447</v>
       </c>
       <c r="J88" t="n">
-        <v>4.4828</v>
+        <v>4.0516</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1601</v>
+        <v>0.1447</v>
       </c>
       <c r="J89" t="n">
-        <v>4.4828</v>
+        <v>4.0516</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0292</v>
+        <v>-0.0207</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.8176</v>
+        <v>-0.5796</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0625</v>
+        <v>-0.0489</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.75</v>
+        <v>-1.3692</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.85</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1733</v>
+        <v>-0.1577</v>
       </c>
       <c r="J92" t="n">
-        <v>-3.8126</v>
+        <v>-3.4694</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.78</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2459</v>
+        <v>-0.2308</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.4098</v>
+        <v>-5.0776</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3103</v>
+        <v>-0.2957</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.8266</v>
+        <v>-6.5054</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3371</v>
+        <v>-0.323</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.4162</v>
+        <v>-7.106</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4175</v>
+        <v>-0.4076</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.185</v>
+        <v>-8.9672</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3592</v>
+        <v>1.3833</v>
       </c>
       <c r="J97" t="n">
-        <v>29.9024</v>
+        <v>30.4326</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.67</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2739</v>
+        <v>1.2948</v>
       </c>
       <c r="J98" t="n">
-        <v>28.0258</v>
+        <v>28.4856</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.57</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1499</v>
+        <v>1.1684</v>
       </c>
       <c r="J99" t="n">
-        <v>25.2978</v>
+        <v>25.7048</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.29</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6923</v>
+        <v>0.6736</v>
       </c>
       <c r="J100" t="n">
-        <v>15.2306</v>
+        <v>14.8192</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.27</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6514</v>
+        <v>0.6302</v>
       </c>
       <c r="J101" t="n">
-        <v>14.3308</v>
+        <v>13.8644</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4553</v>
+        <v>0.3989</v>
       </c>
       <c r="J102" t="n">
-        <v>12.2931</v>
+        <v>10.7703</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1854</v>
+        <v>0.1456</v>
       </c>
       <c r="J103" t="n">
-        <v>5.0058</v>
+        <v>3.9312</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1387</v>
+        <v>0.1052</v>
       </c>
       <c r="J104" t="n">
-        <v>3.7449</v>
+        <v>2.8404</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.79</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2547</v>
+        <v>-0.2351</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.8769</v>
+        <v>-6.3477</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5082</v>
+        <v>-0.51</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.7214</v>
+        <v>-13.77</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0662</v>
+        <v>1.0745</v>
       </c>
       <c r="J107" t="n">
-        <v>28.7874</v>
+        <v>29.0115</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7704</v>
+        <v>0.742</v>
       </c>
       <c r="J108" t="n">
-        <v>20.8008</v>
+        <v>20.034</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7497</v>
+        <v>0.7199</v>
       </c>
       <c r="J109" t="n">
-        <v>20.2419</v>
+        <v>19.4373</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6572</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>-17.7444</v>
+        <v>-16.8345</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6572</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.7444</v>
+        <v>-16.8345</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0602</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.835</v>
+        <v>-1.505</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1582</v>
+        <v>-0.1426</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.955</v>
+        <v>-3.565</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2506</v>
+        <v>-0.2342</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.265</v>
+        <v>-5.855</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.378</v>
+        <v>-0.365</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.125</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.59</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4226</v>
+        <v>-0.413</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.565</v>
+        <v>-10.325</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.67</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3008</v>
+        <v>1.3202</v>
       </c>
       <c r="J117" t="n">
-        <v>32.52</v>
+        <v>33.005</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.48</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0523</v>
+        <v>1.0605</v>
       </c>
       <c r="J118" t="n">
-        <v>26.3075</v>
+        <v>26.5125</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.755</v>
+        <v>0.7348</v>
       </c>
       <c r="J119" t="n">
-        <v>18.875</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.23</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5651</v>
       </c>
       <c r="J120" t="n">
-        <v>14.805</v>
+        <v>14.1275</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1161</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.9025</v>
+        <v>-2.4275</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6011</v>
+        <v>0.5508</v>
       </c>
       <c r="J122" t="n">
-        <v>14.4264</v>
+        <v>13.2192</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.3904</v>
+        <v>-2.0544</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2479</v>
+        <v>-0.229</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.9496</v>
+        <v>-5.496</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3145</v>
+        <v>-0.2973</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.548</v>
+        <v>-7.1352</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.476</v>
+        <v>-0.4726</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.424</v>
+        <v>-11.3424</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.76</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4354</v>
+        <v>1.4642</v>
       </c>
       <c r="J127" t="n">
-        <v>34.4496</v>
+        <v>35.1408</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.48</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0669</v>
+        <v>1.0752</v>
       </c>
       <c r="J128" t="n">
-        <v>25.6056</v>
+        <v>25.8048</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.34</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8236</v>
+        <v>0.8027</v>
       </c>
       <c r="J129" t="n">
-        <v>19.7664</v>
+        <v>19.2648</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3614</v>
+        <v>-0.3217</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.6736</v>
+        <v>-7.7208</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.75</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7449</v>
+        <v>-0.7211</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.8776</v>
+        <v>-17.3064</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.74</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2646</v>
+        <v>-0.2515</v>
       </c>
       <c r="J132" t="n">
-        <v>-5.292</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.67</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3329</v>
+        <v>-0.3229</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.658</v>
+        <v>-6.458</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.6</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3943</v>
+        <v>-0.3861</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.886</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3943</v>
+        <v>-0.3861</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.886</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5515</v>
+        <v>-0.5557</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.03</v>
+        <v>-11.114</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.92</v>
       </c>
       <c r="I137" t="n">
-        <v>1.568</v>
+        <v>1.6047</v>
       </c>
       <c r="J137" t="n">
-        <v>31.36</v>
+        <v>32.094</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.85</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4859</v>
+        <v>1.5172</v>
       </c>
       <c r="J138" t="n">
-        <v>29.718</v>
+        <v>30.344</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.75</v>
       </c>
       <c r="I139" t="n">
-        <v>1.3669</v>
+        <v>1.392</v>
       </c>
       <c r="J139" t="n">
-        <v>27.338</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.12</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3095</v>
+        <v>0.275</v>
       </c>
       <c r="J140" t="n">
-        <v>6.19</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1475</v>
+        <v>0.1152</v>
       </c>
       <c r="J141" t="n">
-        <v>2.95</v>
+        <v>2.304</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5381</v>
+        <v>0.481</v>
       </c>
       <c r="J142" t="n">
-        <v>13.9906</v>
+        <v>12.506</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.3722</v>
+        <v>-2.9146</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.141</v>
+        <v>-0.1227</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.666</v>
+        <v>-3.1902</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2357</v>
+        <v>-0.2157</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.1282</v>
+        <v>-5.6082</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.275</v>
+        <v>-0.2559</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.15</v>
+        <v>-6.6534</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8129</v>
       </c>
       <c r="J147" t="n">
-        <v>21.7152</v>
+        <v>21.1354</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8153</v>
+        <v>0.7916</v>
       </c>
       <c r="J148" t="n">
-        <v>21.1978</v>
+        <v>20.5816</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4808</v>
+        <v>0.4457</v>
       </c>
       <c r="J149" t="n">
-        <v>12.5008</v>
+        <v>11.5882</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3118</v>
+        <v>0.2788</v>
       </c>
       <c r="J150" t="n">
-        <v>8.1068</v>
+        <v>7.2488</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I151" t="n">
-        <v>0.028</v>
+        <v>0.0182</v>
       </c>
       <c r="J151" t="n">
-        <v>0.728</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6052</v>
       </c>
       <c r="J152" t="n">
-        <v>19.914</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4912</v>
+        <v>0.4321</v>
       </c>
       <c r="J153" t="n">
-        <v>14.736</v>
+        <v>12.963</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3205</v>
+        <v>0.2691</v>
       </c>
       <c r="J154" t="n">
-        <v>9.615</v>
+        <v>8.073</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2756</v>
+        <v>-0.2568</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.268000000000001</v>
+        <v>-7.704</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3603</v>
+        <v>-0.3468</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.809</v>
+        <v>-10.404</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6455</v>
+        <v>0.6088</v>
       </c>
       <c r="J157" t="n">
-        <v>19.365</v>
+        <v>18.264</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3082</v>
+        <v>0.2685</v>
       </c>
       <c r="J158" t="n">
-        <v>9.246</v>
+        <v>8.055</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2246</v>
+        <v>0.1896</v>
       </c>
       <c r="J159" t="n">
-        <v>6.738</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2939</v>
+        <v>-0.2531</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.817</v>
+        <v>-7.593</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4509</v>
+        <v>-0.4079</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.527</v>
+        <v>-12.237</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7865</v>
+        <v>0.7595</v>
       </c>
       <c r="J162" t="n">
-        <v>22.8085</v>
+        <v>22.0255</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7659</v>
+        <v>0.7376</v>
       </c>
       <c r="J163" t="n">
-        <v>22.2111</v>
+        <v>21.3904</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6186</v>
+        <v>0.5831</v>
       </c>
       <c r="J164" t="n">
-        <v>17.9394</v>
+        <v>16.9099</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.97</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1607</v>
+        <v>-0.1292</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.6603</v>
+        <v>-3.7468</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3957</v>
+        <v>-0.3534</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.4753</v>
+        <v>-10.2486</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1634</v>
+        <v>0.1265</v>
       </c>
       <c r="J167" t="n">
-        <v>4.7386</v>
+        <v>3.6685</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1143</v>
+        <v>0.0848</v>
       </c>
       <c r="J168" t="n">
-        <v>3.3147</v>
+        <v>2.4592</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.551</v>
+        <v>-0.406</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2042</v>
+        <v>-0.1842</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9218</v>
+        <v>-5.3418</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3673</v>
+        <v>-0.3534</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.6517</v>
+        <v>-10.2486</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6649</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>18.6172</v>
+        <v>16.9792</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6496</v>
+        <v>0.5908</v>
       </c>
       <c r="J173" t="n">
-        <v>18.1888</v>
+        <v>16.5424</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1019</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.8532</v>
+        <v>-2.366</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1266</v>
+        <v>-0.1077</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.5448</v>
+        <v>-3.0156</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4138</v>
+        <v>-0.4054</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.5864</v>
+        <v>-11.3512</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1277</v>
+        <v>1.1404</v>
       </c>
       <c r="J177" t="n">
-        <v>31.5756</v>
+        <v>31.9312</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.36</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8633</v>
       </c>
       <c r="J178" t="n">
-        <v>24.7128</v>
+        <v>24.1724</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0261</v>
+        <v>-0.0206</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.7308</v>
+        <v>-0.5768</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.164</v>
+        <v>-0.1324</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.592</v>
+        <v>-3.7072</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.95</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2297</v>
+        <v>-0.1928</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.4316</v>
+        <v>-5.3984</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8293</v>
+        <v>0.8052</v>
       </c>
       <c r="J182" t="n">
-        <v>23.2204</v>
+        <v>22.5456</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.2</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5546</v>
+        <v>0.517</v>
       </c>
       <c r="J183" t="n">
-        <v>15.5288</v>
+        <v>14.476</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5098</v>
+        <v>0.4717</v>
       </c>
       <c r="J184" t="n">
-        <v>14.2744</v>
+        <v>13.2076</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0214</v>
+        <v>-0.0162</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.5992</v>
+        <v>-0.4536</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.225</v>
+        <v>-0.1879</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.3</v>
+        <v>-5.2612</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4747</v>
+        <v>0.4165</v>
       </c>
       <c r="J187" t="n">
-        <v>13.2916</v>
+        <v>11.662</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4406</v>
+        <v>0.3831</v>
       </c>
       <c r="J188" t="n">
-        <v>12.3368</v>
+        <v>10.7268</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.88</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1668</v>
+        <v>-0.1468</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.6704</v>
+        <v>-4.1104</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2399</v>
+        <v>-0.2197</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.7172</v>
+        <v>-6.1516</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2984</v>
+        <v>-0.2803</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.3552</v>
+        <v>-7.8484</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.145</v>
+        <v>1.1589</v>
       </c>
       <c r="J192" t="n">
-        <v>25.19</v>
+        <v>25.4958</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.45</v>
       </c>
       <c r="I193" t="n">
-        <v>1.007</v>
+        <v>1.0089</v>
       </c>
       <c r="J193" t="n">
-        <v>22.154</v>
+        <v>22.1958</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.33</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7748</v>
       </c>
       <c r="J194" t="n">
-        <v>17.4416</v>
+        <v>17.0456</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.24</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6126</v>
+        <v>0.5863</v>
       </c>
       <c r="J195" t="n">
-        <v>13.4772</v>
+        <v>12.8986</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.14</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3878</v>
+        <v>0.356</v>
       </c>
       <c r="J196" t="n">
-        <v>8.531599999999999</v>
+        <v>7.832</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0619</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.6478</v>
+        <v>-1.3618</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2223</v>
+        <v>-0.2059</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.8906</v>
+        <v>-4.5298</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2322</v>
+        <v>-0.2157</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.1084</v>
+        <v>-4.7454</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2512</v>
+        <v>-0.2346</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.5264</v>
+        <v>-5.1612</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.53</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4764</v>
+        <v>-0.4724</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.4808</v>
+        <v>-10.3928</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.62</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2574</v>
+        <v>1.2749</v>
       </c>
       <c r="J202" t="n">
-        <v>35.2072</v>
+        <v>35.6972</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.49</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0831</v>
+        <v>1.093</v>
       </c>
       <c r="J203" t="n">
-        <v>30.3268</v>
+        <v>30.604</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.08</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2507</v>
+        <v>0.2202</v>
       </c>
       <c r="J204" t="n">
-        <v>7.0196</v>
+        <v>6.1656</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.03</v>
       </c>
       <c r="I205" t="n">
-        <v>0.098</v>
+        <v>0.0775</v>
       </c>
       <c r="J205" t="n">
-        <v>2.744</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.96</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2116</v>
+        <v>-0.1778</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.9248</v>
+        <v>-4.9784</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0019</v>
+        <v>0.0045</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.0532</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.91</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1171</v>
+        <v>-0.1025</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.2788</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.8</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2342</v>
+        <v>-0.2168</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.5576</v>
+        <v>-6.0704</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2528</v>
+        <v>-0.2353</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.0784</v>
+        <v>-6.5884</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4967</v>
+        <v>-0.4954</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.9076</v>
+        <v>-13.8712</v>
       </c>
     </row>
   </sheetData>
